--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -2561,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713706</v>
+        <v>119713686</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
         <v>468414</v>
       </c>
       <c r="R20" t="n">
-        <v>7078867</v>
+        <v>7078890</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713686</v>
+        <v>119713712</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>91128</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,25 +2675,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468414</v>
+        <v>468491</v>
       </c>
       <c r="R21" t="n">
-        <v>7078890</v>
+        <v>7078902</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713712</v>
+        <v>119713706</v>
       </c>
       <c r="B22" t="n">
-        <v>91128</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,25 +2777,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468491</v>
+        <v>468414</v>
       </c>
       <c r="R22" t="n">
-        <v>7078902</v>
+        <v>7078867</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713677</v>
+        <v>119713673</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,21 +2883,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468207</v>
+        <v>468436</v>
       </c>
       <c r="R23" t="n">
-        <v>7078579</v>
+        <v>7079043</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713673</v>
+        <v>119713677</v>
       </c>
       <c r="B24" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,21 +2985,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468436</v>
+        <v>468207</v>
       </c>
       <c r="R24" t="n">
-        <v>7079043</v>
+        <v>7078579</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713632</v>
+        <v>119713692</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468387</v>
+        <v>468377</v>
       </c>
       <c r="R28" t="n">
-        <v>7078261</v>
+        <v>7078959</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,11 +3468,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3499,10 +3494,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713630</v>
+        <v>119713704</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3515,21 +3510,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3539,10 +3534,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468507</v>
+        <v>468356</v>
       </c>
       <c r="R29" t="n">
-        <v>7078135</v>
+        <v>7077992</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3575,11 +3570,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3606,7 +3596,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713625</v>
+        <v>119713632</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3646,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468255</v>
+        <v>468387</v>
       </c>
       <c r="R30" t="n">
-        <v>7078014</v>
+        <v>7078261</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,7 +3676,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3713,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713704</v>
+        <v>119713630</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3729,21 +3719,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3753,10 +3743,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468356</v>
+        <v>468507</v>
       </c>
       <c r="R31" t="n">
-        <v>7077992</v>
+        <v>7078135</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,6 +3779,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3815,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713692</v>
+        <v>119713625</v>
       </c>
       <c r="B32" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3831,21 +3826,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3855,10 +3850,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468377</v>
+        <v>468255</v>
       </c>
       <c r="R32" t="n">
-        <v>7078959</v>
+        <v>7078014</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,6 +3886,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4544,10 +4544,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119713680</v>
+        <v>119713663</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468356</v>
+        <v>468431</v>
       </c>
       <c r="R39" t="n">
-        <v>7078372</v>
+        <v>7079071</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4620,6 +4620,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4646,7 +4651,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119713663</v>
+        <v>119713631</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4686,10 +4691,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468431</v>
+        <v>468508</v>
       </c>
       <c r="R40" t="n">
-        <v>7079071</v>
+        <v>7078150</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4753,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119713631</v>
+        <v>119713680</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4769,21 +4774,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4793,10 +4798,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468508</v>
+        <v>468356</v>
       </c>
       <c r="R41" t="n">
-        <v>7078150</v>
+        <v>7078372</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4829,11 +4834,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713676</v>
+        <v>119713611</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468277</v>
+        <v>468510</v>
       </c>
       <c r="R8" t="n">
-        <v>7078898</v>
+        <v>7078916</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713691</v>
+        <v>119713661</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468394</v>
+        <v>468387</v>
       </c>
       <c r="R9" t="n">
-        <v>7078944</v>
+        <v>7078948</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713698</v>
+        <v>119713676</v>
       </c>
       <c r="B10" t="n">
         <v>79607</v>
@@ -1551,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468338</v>
+        <v>468277</v>
       </c>
       <c r="R10" t="n">
-        <v>7079023</v>
+        <v>7078898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713611</v>
+        <v>119713691</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468510</v>
+        <v>468394</v>
       </c>
       <c r="R11" t="n">
-        <v>7078916</v>
+        <v>7078944</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713661</v>
+        <v>119713698</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468387</v>
+        <v>468338</v>
       </c>
       <c r="R12" t="n">
-        <v>7078948</v>
+        <v>7079023</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2561,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713686</v>
+        <v>119713706</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
         <v>468414</v>
       </c>
       <c r="R20" t="n">
-        <v>7078890</v>
+        <v>7078867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713712</v>
+        <v>119713686</v>
       </c>
       <c r="B21" t="n">
-        <v>91128</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,25 +2675,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468491</v>
+        <v>468414</v>
       </c>
       <c r="R21" t="n">
-        <v>7078902</v>
+        <v>7078890</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713706</v>
+        <v>119713712</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>91128</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,25 +2777,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468414</v>
+        <v>468491</v>
       </c>
       <c r="R22" t="n">
-        <v>7078867</v>
+        <v>7078902</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713684</v>
+        <v>119713682</v>
       </c>
       <c r="B3" t="n">
         <v>79607</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468525</v>
+        <v>468392</v>
       </c>
       <c r="R3" t="n">
-        <v>7078870</v>
+        <v>7078534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713620</v>
+        <v>119713633</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468251</v>
+        <v>468383</v>
       </c>
       <c r="R4" t="n">
-        <v>7078667</v>
+        <v>7078394</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713648</v>
+        <v>119713630</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468397</v>
+        <v>468507</v>
       </c>
       <c r="R5" t="n">
-        <v>7078890</v>
+        <v>7078135</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713612</v>
+        <v>119713683</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468171</v>
+        <v>468440</v>
       </c>
       <c r="R6" t="n">
-        <v>7079106</v>
+        <v>7078819</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713629</v>
+        <v>119713681</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468444</v>
+        <v>468360</v>
       </c>
       <c r="R7" t="n">
-        <v>7078147</v>
+        <v>7078504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713611</v>
+        <v>119713645</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468510</v>
+        <v>468491</v>
       </c>
       <c r="R8" t="n">
-        <v>7078916</v>
+        <v>7078873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713661</v>
+        <v>119713637</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1454,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468387</v>
+        <v>468382</v>
       </c>
       <c r="R9" t="n">
-        <v>7078948</v>
+        <v>7078551</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713676</v>
+        <v>119713609</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468277</v>
+        <v>468506</v>
       </c>
       <c r="R10" t="n">
-        <v>7078898</v>
+        <v>7078126</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713691</v>
+        <v>119713703</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>90558</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468394</v>
+        <v>468369</v>
       </c>
       <c r="R11" t="n">
-        <v>7078944</v>
+        <v>7078973</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713698</v>
+        <v>119713712</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>91128</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468338</v>
+        <v>468491</v>
       </c>
       <c r="R12" t="n">
-        <v>7079023</v>
+        <v>7078902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713708</v>
+        <v>119713705</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468354</v>
+        <v>468432</v>
       </c>
       <c r="R13" t="n">
-        <v>7078051</v>
+        <v>7078079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,11 +1893,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713682</v>
+        <v>119713695</v>
       </c>
       <c r="B14" t="n">
         <v>79607</v>
@@ -1974,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468392</v>
+        <v>468411</v>
       </c>
       <c r="R14" t="n">
-        <v>7078534</v>
+        <v>7078994</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713609</v>
+        <v>119713699</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468506</v>
+        <v>468287</v>
       </c>
       <c r="R15" t="n">
-        <v>7078126</v>
+        <v>7079069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713679</v>
+        <v>119713646</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468408</v>
+        <v>468500</v>
       </c>
       <c r="R16" t="n">
-        <v>7078270</v>
+        <v>7078848</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713709</v>
+        <v>119713654</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468530</v>
+        <v>468493</v>
       </c>
       <c r="R17" t="n">
-        <v>7078853</v>
+        <v>7078945</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2310,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713647</v>
+        <v>119713673</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2363,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2387,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468481</v>
+        <v>468436</v>
       </c>
       <c r="R18" t="n">
-        <v>7078859</v>
+        <v>7079043</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,7 +2439,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713635</v>
+        <v>119713623</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2494,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468498</v>
+        <v>468342</v>
       </c>
       <c r="R19" t="n">
-        <v>7078513</v>
+        <v>7078288</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713706</v>
+        <v>119713618</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468414</v>
+        <v>468315</v>
       </c>
       <c r="R20" t="n">
-        <v>7078867</v>
+        <v>7078711</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,6 +2622,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713686</v>
+        <v>119713631</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,21 +2669,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468414</v>
+        <v>468508</v>
       </c>
       <c r="R21" t="n">
-        <v>7078890</v>
+        <v>7078150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,6 +2729,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2765,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713712</v>
+        <v>119713625</v>
       </c>
       <c r="B22" t="n">
-        <v>91128</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,25 +2772,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468491</v>
+        <v>468255</v>
       </c>
       <c r="R22" t="n">
-        <v>7078902</v>
+        <v>7078014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,6 +2836,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713673</v>
+        <v>119713634</v>
       </c>
       <c r="B23" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,21 +2883,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468436</v>
+        <v>468498</v>
       </c>
       <c r="R23" t="n">
-        <v>7079043</v>
+        <v>7078528</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,6 +2943,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713677</v>
+        <v>119713661</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,21 +2990,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3009,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468207</v>
+        <v>468387</v>
       </c>
       <c r="R24" t="n">
-        <v>7078579</v>
+        <v>7078948</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,6 +3050,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713636</v>
+        <v>119713640</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3111,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468454</v>
+        <v>468538</v>
       </c>
       <c r="R25" t="n">
-        <v>7078551</v>
+        <v>7078860</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3151,7 +3161,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3178,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713627</v>
+        <v>119713677</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3194,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3218,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468420</v>
+        <v>468207</v>
       </c>
       <c r="R26" t="n">
-        <v>7078103</v>
+        <v>7078579</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,11 +3264,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,7 +3290,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119713621</v>
+        <v>119713663</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3325,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468270</v>
+        <v>468431</v>
       </c>
       <c r="R27" t="n">
-        <v>7078423</v>
+        <v>7079071</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3365,7 +3370,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3392,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713692</v>
+        <v>119713666</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3408,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3432,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468377</v>
+        <v>468267</v>
       </c>
       <c r="R28" t="n">
-        <v>7078959</v>
+        <v>7079149</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,6 +3473,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3494,10 +3504,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713704</v>
+        <v>119713676</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3510,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3534,10 +3544,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468356</v>
+        <v>468277</v>
       </c>
       <c r="R29" t="n">
-        <v>7077992</v>
+        <v>7078898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3596,7 +3606,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713632</v>
+        <v>119713626</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3636,10 +3646,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468387</v>
+        <v>468396</v>
       </c>
       <c r="R30" t="n">
-        <v>7078261</v>
+        <v>7078010</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3676,7 +3686,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,7 +3713,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713630</v>
+        <v>119713664</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3743,10 +3753,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468507</v>
+        <v>468402</v>
       </c>
       <c r="R31" t="n">
-        <v>7078135</v>
+        <v>7079059</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3783,7 +3793,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3810,7 +3820,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713625</v>
+        <v>119713612</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3850,10 +3860,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468255</v>
+        <v>468171</v>
       </c>
       <c r="R32" t="n">
-        <v>7078014</v>
+        <v>7079106</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,7 +3900,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713710</v>
+        <v>119713616</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3933,21 +3943,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3957,10 +3967,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468311</v>
+        <v>468263</v>
       </c>
       <c r="R33" t="n">
-        <v>7079041</v>
+        <v>7078968</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3997,7 +4007,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713689</v>
+        <v>119713652</v>
       </c>
       <c r="B34" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4040,21 +4050,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4064,10 +4074,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468428</v>
+        <v>468431</v>
       </c>
       <c r="R34" t="n">
-        <v>7078967</v>
+        <v>7078899</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4100,6 +4110,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4126,10 +4141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713675</v>
+        <v>119713617</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4142,21 +4157,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4166,10 +4181,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>468269</v>
+        <v>468290</v>
       </c>
       <c r="R35" t="n">
-        <v>7078942</v>
+        <v>7078881</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4202,6 +4217,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4228,7 +4248,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119713643</v>
+        <v>119713667</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4268,10 +4288,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>468546</v>
+        <v>468260</v>
       </c>
       <c r="R36" t="n">
-        <v>7078893</v>
+        <v>7079151</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4335,7 +4355,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119713622</v>
+        <v>119713657</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4375,10 +4395,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>468259</v>
+        <v>468462</v>
       </c>
       <c r="R37" t="n">
-        <v>7078432</v>
+        <v>7078991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4442,10 +4462,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119713714</v>
+        <v>119713680</v>
       </c>
       <c r="B38" t="n">
-        <v>86878</v>
+        <v>79607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4458,21 +4478,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4482,10 +4502,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468340</v>
+        <v>468356</v>
       </c>
       <c r="R38" t="n">
-        <v>7078142</v>
+        <v>7078372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4544,10 +4564,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119713663</v>
+        <v>119713708</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4560,21 +4580,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4584,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468431</v>
+        <v>468354</v>
       </c>
       <c r="R39" t="n">
-        <v>7079071</v>
+        <v>7078051</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4624,7 +4644,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4651,7 +4671,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119713631</v>
+        <v>119713647</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4691,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468508</v>
+        <v>468481</v>
       </c>
       <c r="R40" t="n">
-        <v>7078150</v>
+        <v>7078859</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4731,7 +4751,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4758,10 +4778,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119713680</v>
+        <v>119713662</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4774,21 +4794,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4798,10 +4818,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468356</v>
+        <v>468406</v>
       </c>
       <c r="R41" t="n">
-        <v>7078372</v>
+        <v>7078996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4834,6 +4854,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4860,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119713711</v>
+        <v>119713641</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4876,21 +4901,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4900,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468242</v>
+        <v>468546</v>
       </c>
       <c r="R42" t="n">
-        <v>7079178</v>
+        <v>7078889</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4940,7 +4965,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4967,10 +4992,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119713646</v>
+        <v>119713693</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4983,21 +5008,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5007,10 +5032,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468500</v>
+        <v>468379</v>
       </c>
       <c r="R43" t="n">
-        <v>7078848</v>
+        <v>7078971</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5043,11 +5068,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5074,7 +5094,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119713667</v>
+        <v>119713643</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5114,10 +5134,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468260</v>
+        <v>468546</v>
       </c>
       <c r="R44" t="n">
-        <v>7079151</v>
+        <v>7078893</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5181,7 +5201,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119713614</v>
+        <v>119713621</v>
       </c>
       <c r="B45" t="n">
         <v>57310</v>
@@ -5221,10 +5241,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468271</v>
+        <v>468270</v>
       </c>
       <c r="R45" t="n">
-        <v>7079042</v>
+        <v>7078423</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5308,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119713705</v>
+        <v>119713611</v>
       </c>
       <c r="B46" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,21 +5324,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5328,10 +5348,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468432</v>
+        <v>468510</v>
       </c>
       <c r="R46" t="n">
-        <v>7078079</v>
+        <v>7078916</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5364,6 +5384,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5390,10 +5415,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119713678</v>
+        <v>119713649</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5406,21 +5431,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5430,10 +5455,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468305</v>
+        <v>468392</v>
       </c>
       <c r="R47" t="n">
-        <v>7078326</v>
+        <v>7078891</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5466,6 +5491,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5492,7 +5522,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119713637</v>
+        <v>119713665</v>
       </c>
       <c r="B48" t="n">
         <v>57310</v>
@@ -5532,10 +5562,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468382</v>
+        <v>468309</v>
       </c>
       <c r="R48" t="n">
-        <v>7078551</v>
+        <v>7079036</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5572,7 +5602,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5599,10 +5629,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119713666</v>
+        <v>119713689</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5615,21 +5645,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5669,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468267</v>
+        <v>468428</v>
       </c>
       <c r="R49" t="n">
-        <v>7079149</v>
+        <v>7078967</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5675,11 +5705,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5706,7 +5731,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119713628</v>
+        <v>119713622</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5746,10 +5771,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468442</v>
+        <v>468259</v>
       </c>
       <c r="R50" t="n">
-        <v>7078110</v>
+        <v>7078432</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5813,10 +5838,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119713634</v>
+        <v>119713694</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5829,21 +5854,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5853,10 +5878,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468498</v>
+        <v>468358</v>
       </c>
       <c r="R51" t="n">
-        <v>7078528</v>
+        <v>7078970</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5889,11 +5914,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5920,7 +5940,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119713685</v>
+        <v>119713697</v>
       </c>
       <c r="B52" t="n">
         <v>79607</v>
@@ -5960,10 +5980,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468491</v>
+        <v>468436</v>
       </c>
       <c r="R52" t="n">
-        <v>7078903</v>
+        <v>7079043</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6022,10 +6042,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119713660</v>
+        <v>119713675</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6038,21 +6058,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6062,10 +6082,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468411</v>
+        <v>468269</v>
       </c>
       <c r="R53" t="n">
-        <v>7078960</v>
+        <v>7078942</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6098,11 +6118,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6129,10 +6144,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119713650</v>
+        <v>119713710</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6145,21 +6160,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6169,10 +6184,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468408</v>
+        <v>468311</v>
       </c>
       <c r="R54" t="n">
-        <v>7078892</v>
+        <v>7079041</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,7 +6224,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6236,10 +6251,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119713654</v>
+        <v>119713707</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6252,21 +6267,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6276,10 +6291,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468493</v>
+        <v>468344</v>
       </c>
       <c r="R55" t="n">
-        <v>7078945</v>
+        <v>7078143</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6316,7 +6331,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6343,7 +6358,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119713665</v>
+        <v>119713635</v>
       </c>
       <c r="B56" t="n">
         <v>57310</v>
@@ -6383,10 +6398,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468309</v>
+        <v>468498</v>
       </c>
       <c r="R56" t="n">
-        <v>7079036</v>
+        <v>7078513</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6423,7 +6438,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6450,7 +6465,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119713626</v>
+        <v>119713629</v>
       </c>
       <c r="B57" t="n">
         <v>57310</v>
@@ -6490,10 +6505,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468396</v>
+        <v>468444</v>
       </c>
       <c r="R57" t="n">
-        <v>7078010</v>
+        <v>7078147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6557,7 +6572,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119713649</v>
+        <v>119713638</v>
       </c>
       <c r="B58" t="n">
         <v>57310</v>
@@ -6597,10 +6612,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468392</v>
+        <v>468450</v>
       </c>
       <c r="R58" t="n">
-        <v>7078891</v>
+        <v>7078735</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6637,7 +6652,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6664,7 +6679,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119713633</v>
+        <v>119713650</v>
       </c>
       <c r="B59" t="n">
         <v>57310</v>
@@ -6704,10 +6719,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468383</v>
+        <v>468408</v>
       </c>
       <c r="R59" t="n">
-        <v>7078394</v>
+        <v>7078892</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6744,7 +6759,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6771,7 +6786,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119713657</v>
+        <v>119713636</v>
       </c>
       <c r="B60" t="n">
         <v>57310</v>
@@ -6811,10 +6826,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468462</v>
+        <v>468454</v>
       </c>
       <c r="R60" t="n">
-        <v>7078991</v>
+        <v>7078551</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6851,7 +6866,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6878,10 +6893,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119713640</v>
+        <v>119713706</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6894,21 +6909,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6918,10 +6933,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468538</v>
+        <v>468414</v>
       </c>
       <c r="R61" t="n">
-        <v>7078860</v>
+        <v>7078867</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6954,11 +6969,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6985,10 +6995,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119713664</v>
+        <v>119713684</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7001,21 +7011,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7025,10 +7035,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468402</v>
+        <v>468525</v>
       </c>
       <c r="R62" t="n">
-        <v>7079059</v>
+        <v>7078870</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7061,11 +7071,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7092,7 +7097,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119713683</v>
+        <v>119713692</v>
       </c>
       <c r="B63" t="n">
         <v>79607</v>
@@ -7132,10 +7137,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468440</v>
+        <v>468377</v>
       </c>
       <c r="R63" t="n">
-        <v>7078819</v>
+        <v>7078959</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7199,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119713695</v>
+        <v>119713711</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7210,21 +7215,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7234,10 +7239,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468411</v>
+        <v>468242</v>
       </c>
       <c r="R64" t="n">
-        <v>7078994</v>
+        <v>7079178</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7270,6 +7275,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7296,10 +7306,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119713707</v>
+        <v>119713691</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7312,21 +7322,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7336,10 +7346,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468344</v>
+        <v>468394</v>
       </c>
       <c r="R65" t="n">
-        <v>7078143</v>
+        <v>7078944</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7372,11 +7382,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7403,10 +7408,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119713613</v>
+        <v>119713698</v>
       </c>
       <c r="B66" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7419,21 +7424,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7443,10 +7448,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468269</v>
+        <v>468338</v>
       </c>
       <c r="R66" t="n">
-        <v>7079044</v>
+        <v>7079023</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7479,11 +7484,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7510,10 +7510,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119713623</v>
+        <v>119713678</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7526,21 +7526,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468342</v>
+        <v>468305</v>
       </c>
       <c r="R67" t="n">
-        <v>7078288</v>
+        <v>7078326</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7586,11 +7586,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7617,10 +7612,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119713624</v>
+        <v>119713685</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7633,21 +7628,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7657,10 +7652,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468284</v>
+        <v>468491</v>
       </c>
       <c r="R68" t="n">
-        <v>7078113</v>
+        <v>7078903</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7693,11 +7688,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7724,7 +7714,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119713638</v>
+        <v>119713639</v>
       </c>
       <c r="B69" t="n">
         <v>57310</v>
@@ -7764,10 +7754,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468450</v>
+        <v>468440</v>
       </c>
       <c r="R69" t="n">
-        <v>7078735</v>
+        <v>7078822</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7804,7 +7794,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7831,7 +7821,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119713641</v>
+        <v>119713628</v>
       </c>
       <c r="B70" t="n">
         <v>57310</v>
@@ -7871,10 +7861,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468546</v>
+        <v>468442</v>
       </c>
       <c r="R70" t="n">
-        <v>7078889</v>
+        <v>7078110</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7911,7 +7901,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7938,7 +7928,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119713652</v>
+        <v>119713627</v>
       </c>
       <c r="B71" t="n">
         <v>57310</v>
@@ -7978,10 +7968,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468431</v>
+        <v>468420</v>
       </c>
       <c r="R71" t="n">
-        <v>7078899</v>
+        <v>7078103</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8018,7 +8008,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8045,10 +8035,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119713610</v>
+        <v>119713613</v>
       </c>
       <c r="B72" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8061,21 +8051,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8085,10 +8075,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468502</v>
+        <v>468269</v>
       </c>
       <c r="R72" t="n">
-        <v>7078172</v>
+        <v>7079044</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8121,6 +8111,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8147,10 +8142,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119713703</v>
+        <v>119713709</v>
       </c>
       <c r="B73" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8163,21 +8158,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8187,10 +8182,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468369</v>
+        <v>468530</v>
       </c>
       <c r="R73" t="n">
-        <v>7078973</v>
+        <v>7078853</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8223,6 +8218,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8249,10 +8249,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119713694</v>
+        <v>119713704</v>
       </c>
       <c r="B74" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8265,21 +8265,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468358</v>
+        <v>468356</v>
       </c>
       <c r="R74" t="n">
-        <v>7078970</v>
+        <v>7077992</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8351,10 +8351,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119713681</v>
+        <v>119713614</v>
       </c>
       <c r="B75" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8367,21 +8367,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468360</v>
+        <v>468271</v>
       </c>
       <c r="R75" t="n">
-        <v>7078504</v>
+        <v>7079042</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8427,6 +8427,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8453,10 +8458,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119713693</v>
+        <v>119713660</v>
       </c>
       <c r="B76" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8469,21 +8474,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8493,10 +8498,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468379</v>
+        <v>468411</v>
       </c>
       <c r="R76" t="n">
-        <v>7078971</v>
+        <v>7078960</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,6 +8534,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8555,7 +8565,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119713616</v>
+        <v>119713624</v>
       </c>
       <c r="B77" t="n">
         <v>57310</v>
@@ -8595,10 +8605,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468263</v>
+        <v>468284</v>
       </c>
       <c r="R77" t="n">
-        <v>7078968</v>
+        <v>7078113</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8635,7 +8645,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8662,7 +8672,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119713618</v>
+        <v>119713632</v>
       </c>
       <c r="B78" t="n">
         <v>57310</v>
@@ -8702,10 +8712,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468315</v>
+        <v>468387</v>
       </c>
       <c r="R78" t="n">
-        <v>7078711</v>
+        <v>7078261</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8742,7 +8752,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8769,10 +8779,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119713645</v>
+        <v>119713679</v>
       </c>
       <c r="B79" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8785,21 +8795,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8809,10 +8819,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468491</v>
+        <v>468408</v>
       </c>
       <c r="R79" t="n">
-        <v>7078873</v>
+        <v>7078270</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8845,11 +8855,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8876,10 +8881,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119713639</v>
+        <v>119713686</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8892,21 +8897,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8916,10 +8921,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468440</v>
+        <v>468414</v>
       </c>
       <c r="R80" t="n">
-        <v>7078822</v>
+        <v>7078890</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8952,11 +8957,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8983,7 +8983,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119713617</v>
+        <v>119713620</v>
       </c>
       <c r="B81" t="n">
         <v>57310</v>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468290</v>
+        <v>468251</v>
       </c>
       <c r="R81" t="n">
-        <v>7078881</v>
+        <v>7078667</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9090,7 +9090,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119713662</v>
+        <v>119713648</v>
       </c>
       <c r="B82" t="n">
         <v>57310</v>
@@ -9130,10 +9130,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468406</v>
+        <v>468397</v>
       </c>
       <c r="R82" t="n">
-        <v>7078996</v>
+        <v>7078890</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9197,10 +9197,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119713697</v>
+        <v>119713714</v>
       </c>
       <c r="B83" t="n">
-        <v>79607</v>
+        <v>86878</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9213,21 +9213,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9237,10 +9237,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468436</v>
+        <v>468340</v>
       </c>
       <c r="R83" t="n">
-        <v>7079043</v>
+        <v>7078142</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9299,10 +9299,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119713699</v>
+        <v>119713610</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9315,21 +9315,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468287</v>
+        <v>468502</v>
       </c>
       <c r="R84" t="n">
-        <v>7079069</v>
+        <v>7078172</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713687</v>
+        <v>119713683</v>
       </c>
       <c r="B2" t="n">
         <v>79607</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468461</v>
+        <v>468440</v>
       </c>
       <c r="R2" t="n">
-        <v>7078992</v>
+        <v>7078819</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713682</v>
+        <v>119713687</v>
       </c>
       <c r="B3" t="n">
         <v>79607</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468392</v>
+        <v>468461</v>
       </c>
       <c r="R3" t="n">
-        <v>7078534</v>
+        <v>7078992</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713633</v>
+        <v>119713682</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468383</v>
+        <v>468392</v>
       </c>
       <c r="R4" t="n">
-        <v>7078394</v>
+        <v>7078534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713630</v>
+        <v>119713633</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468507</v>
+        <v>468383</v>
       </c>
       <c r="R5" t="n">
-        <v>7078135</v>
+        <v>7078394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713683</v>
+        <v>119713630</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468440</v>
+        <v>468507</v>
       </c>
       <c r="R6" t="n">
-        <v>7078819</v>
+        <v>7078135</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713703</v>
+        <v>119713705</v>
       </c>
       <c r="B11" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468369</v>
+        <v>468432</v>
       </c>
       <c r="R11" t="n">
-        <v>7078973</v>
+        <v>7078079</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713712</v>
+        <v>119713695</v>
       </c>
       <c r="B12" t="n">
-        <v>91128</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468491</v>
+        <v>468411</v>
       </c>
       <c r="R12" t="n">
-        <v>7078902</v>
+        <v>7078994</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713705</v>
+        <v>119713699</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468432</v>
+        <v>468287</v>
       </c>
       <c r="R13" t="n">
-        <v>7078079</v>
+        <v>7079069</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713695</v>
+        <v>119713703</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>90558</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468411</v>
+        <v>468369</v>
       </c>
       <c r="R14" t="n">
-        <v>7078994</v>
+        <v>7078973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713699</v>
+        <v>119713654</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468287</v>
+        <v>468493</v>
       </c>
       <c r="R15" t="n">
-        <v>7079069</v>
+        <v>7078945</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,6 +2097,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713646</v>
+        <v>119713712</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>91128</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2140,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468500</v>
+        <v>468491</v>
       </c>
       <c r="R16" t="n">
-        <v>7078848</v>
+        <v>7078902</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,11 +2204,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,7 +2230,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713654</v>
+        <v>119713646</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468493</v>
+        <v>468500</v>
       </c>
       <c r="R17" t="n">
-        <v>7078945</v>
+        <v>7078848</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -6042,10 +6042,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119713675</v>
+        <v>119713710</v>
       </c>
       <c r="B53" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6058,21 +6058,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468269</v>
+        <v>468311</v>
       </c>
       <c r="R53" t="n">
-        <v>7078942</v>
+        <v>7079041</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6118,6 +6118,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6144,7 +6149,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119713710</v>
+        <v>119713707</v>
       </c>
       <c r="B54" t="n">
         <v>78526</v>
@@ -6184,10 +6189,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468311</v>
+        <v>468344</v>
       </c>
       <c r="R54" t="n">
-        <v>7079041</v>
+        <v>7078143</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6224,7 +6229,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6251,10 +6256,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119713707</v>
+        <v>119713675</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6267,21 +6272,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6291,10 +6296,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468344</v>
+        <v>468269</v>
       </c>
       <c r="R55" t="n">
-        <v>7078143</v>
+        <v>7078942</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6327,11 +6332,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7199,10 +7199,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119713711</v>
+        <v>119713628</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7215,21 +7215,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468242</v>
+        <v>468442</v>
       </c>
       <c r="R64" t="n">
-        <v>7079178</v>
+        <v>7078110</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7306,10 +7306,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119713691</v>
+        <v>119713627</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7322,21 +7322,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468394</v>
+        <v>468420</v>
       </c>
       <c r="R65" t="n">
-        <v>7078944</v>
+        <v>7078103</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7382,6 +7382,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7408,7 +7413,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119713698</v>
+        <v>119713691</v>
       </c>
       <c r="B66" t="n">
         <v>79607</v>
@@ -7448,10 +7453,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468338</v>
+        <v>468394</v>
       </c>
       <c r="R66" t="n">
-        <v>7079023</v>
+        <v>7078944</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7510,7 +7515,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119713678</v>
+        <v>119713698</v>
       </c>
       <c r="B67" t="n">
         <v>79607</v>
@@ -7550,10 +7555,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468305</v>
+        <v>468338</v>
       </c>
       <c r="R67" t="n">
-        <v>7078326</v>
+        <v>7079023</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7612,7 +7617,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119713685</v>
+        <v>119713678</v>
       </c>
       <c r="B68" t="n">
         <v>79607</v>
@@ -7652,10 +7657,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468491</v>
+        <v>468305</v>
       </c>
       <c r="R68" t="n">
-        <v>7078903</v>
+        <v>7078326</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7714,10 +7719,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119713639</v>
+        <v>119713685</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7730,21 +7735,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7754,10 +7759,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468440</v>
+        <v>468491</v>
       </c>
       <c r="R69" t="n">
-        <v>7078822</v>
+        <v>7078903</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7790,11 +7795,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7821,10 +7821,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119713628</v>
+        <v>119713711</v>
       </c>
       <c r="B70" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7837,21 +7837,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468442</v>
+        <v>468242</v>
       </c>
       <c r="R70" t="n">
-        <v>7078110</v>
+        <v>7079178</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7928,7 +7928,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119713627</v>
+        <v>119713639</v>
       </c>
       <c r="B71" t="n">
         <v>57310</v>
@@ -7968,10 +7968,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468420</v>
+        <v>468440</v>
       </c>
       <c r="R71" t="n">
-        <v>7078103</v>
+        <v>7078822</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119713614</v>
+        <v>119713679</v>
       </c>
       <c r="B75" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8367,21 +8367,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468271</v>
+        <v>468408</v>
       </c>
       <c r="R75" t="n">
-        <v>7079042</v>
+        <v>7078270</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8427,11 +8427,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8458,10 +8453,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119713660</v>
+        <v>119713686</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8474,21 +8469,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8498,10 +8493,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468411</v>
+        <v>468414</v>
       </c>
       <c r="R76" t="n">
-        <v>7078960</v>
+        <v>7078890</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8534,11 +8529,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8565,7 +8555,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119713624</v>
+        <v>119713614</v>
       </c>
       <c r="B77" t="n">
         <v>57310</v>
@@ -8605,10 +8595,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468284</v>
+        <v>468271</v>
       </c>
       <c r="R77" t="n">
-        <v>7078113</v>
+        <v>7079042</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8645,7 +8635,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8672,7 +8662,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119713632</v>
+        <v>119713660</v>
       </c>
       <c r="B78" t="n">
         <v>57310</v>
@@ -8712,10 +8702,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468387</v>
+        <v>468411</v>
       </c>
       <c r="R78" t="n">
-        <v>7078261</v>
+        <v>7078960</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8779,10 +8769,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119713679</v>
+        <v>119713624</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8795,21 +8785,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8819,10 +8809,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468408</v>
+        <v>468284</v>
       </c>
       <c r="R79" t="n">
-        <v>7078270</v>
+        <v>7078113</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8855,6 +8845,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8881,10 +8876,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119713686</v>
+        <v>119713632</v>
       </c>
       <c r="B80" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8897,21 +8892,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8921,10 +8916,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468414</v>
+        <v>468387</v>
       </c>
       <c r="R80" t="n">
-        <v>7078890</v>
+        <v>7078261</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8957,6 +8952,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8983,10 +8983,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119713620</v>
+        <v>119713714</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>86878</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8999,21 +8999,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468251</v>
+        <v>468340</v>
       </c>
       <c r="R81" t="n">
-        <v>7078667</v>
+        <v>7078142</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9059,11 +9059,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9090,10 +9085,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119713648</v>
+        <v>119713610</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9106,21 +9101,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9130,10 +9125,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468397</v>
+        <v>468502</v>
       </c>
       <c r="R82" t="n">
-        <v>7078890</v>
+        <v>7078172</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9166,11 +9161,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9197,10 +9187,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119713714</v>
+        <v>119713620</v>
       </c>
       <c r="B83" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9213,21 +9203,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9237,10 +9227,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468340</v>
+        <v>468251</v>
       </c>
       <c r="R83" t="n">
-        <v>7078142</v>
+        <v>7078667</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9273,6 +9263,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9299,10 +9294,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119713610</v>
+        <v>119713648</v>
       </c>
       <c r="B84" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9315,21 +9310,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9339,10 +9334,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468502</v>
+        <v>468397</v>
       </c>
       <c r="R84" t="n">
-        <v>7078172</v>
+        <v>7078890</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9375,6 +9370,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713683</v>
+        <v>119713636</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468440</v>
+        <v>468454</v>
       </c>
       <c r="R2" t="n">
-        <v>7078819</v>
+        <v>7078551</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713687</v>
+        <v>119713647</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468461</v>
+        <v>468481</v>
       </c>
       <c r="R3" t="n">
-        <v>7078992</v>
+        <v>7078859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713682</v>
+        <v>119713645</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468392</v>
+        <v>468491</v>
       </c>
       <c r="R4" t="n">
-        <v>7078534</v>
+        <v>7078873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713633</v>
+        <v>119713613</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1021,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468383</v>
+        <v>468269</v>
       </c>
       <c r="R5" t="n">
-        <v>7078394</v>
+        <v>7079044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713630</v>
+        <v>119713634</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1128,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468507</v>
+        <v>468498</v>
       </c>
       <c r="R6" t="n">
-        <v>7078135</v>
+        <v>7078528</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713681</v>
+        <v>119713709</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468360</v>
+        <v>468530</v>
       </c>
       <c r="R7" t="n">
-        <v>7078504</v>
+        <v>7078853</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713645</v>
+        <v>119713714</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>86878</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468491</v>
+        <v>468340</v>
       </c>
       <c r="R8" t="n">
-        <v>7078873</v>
+        <v>7078142</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713637</v>
+        <v>119713712</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>91128</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1431,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468382</v>
+        <v>468491</v>
       </c>
       <c r="R9" t="n">
-        <v>7078551</v>
+        <v>7078902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713609</v>
+        <v>119713628</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468506</v>
+        <v>468442</v>
       </c>
       <c r="R10" t="n">
-        <v>7078126</v>
+        <v>7078110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713705</v>
+        <v>119713652</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468432</v>
+        <v>468431</v>
       </c>
       <c r="R11" t="n">
-        <v>7078079</v>
+        <v>7078899</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713695</v>
+        <v>119713673</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468411</v>
+        <v>468436</v>
       </c>
       <c r="R12" t="n">
-        <v>7078994</v>
+        <v>7079043</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713699</v>
+        <v>119713682</v>
       </c>
       <c r="B13" t="n">
         <v>79607</v>
@@ -1857,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468287</v>
+        <v>468392</v>
       </c>
       <c r="R13" t="n">
-        <v>7079069</v>
+        <v>7078534</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713703</v>
+        <v>119713675</v>
       </c>
       <c r="B14" t="n">
-        <v>90558</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468369</v>
+        <v>468269</v>
       </c>
       <c r="R14" t="n">
-        <v>7078973</v>
+        <v>7078942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713654</v>
+        <v>119713706</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468493</v>
+        <v>468414</v>
       </c>
       <c r="R15" t="n">
-        <v>7078945</v>
+        <v>7078867</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,11 +2117,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713712</v>
+        <v>119713626</v>
       </c>
       <c r="B16" t="n">
-        <v>91128</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2140,25 +2155,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468491</v>
+        <v>468396</v>
       </c>
       <c r="R16" t="n">
-        <v>7078902</v>
+        <v>7078010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,6 +2219,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713646</v>
+        <v>119713650</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2270,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468500</v>
+        <v>468408</v>
       </c>
       <c r="R17" t="n">
-        <v>7078848</v>
+        <v>7078892</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2330,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713673</v>
+        <v>119713631</v>
       </c>
       <c r="B18" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2373,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468436</v>
+        <v>468508</v>
       </c>
       <c r="R18" t="n">
-        <v>7079043</v>
+        <v>7078150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,6 +2433,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713623</v>
+        <v>119713661</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2479,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468342</v>
+        <v>468387</v>
       </c>
       <c r="R19" t="n">
-        <v>7078288</v>
+        <v>7078948</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,7 +2544,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713618</v>
+        <v>119713679</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468315</v>
+        <v>468408</v>
       </c>
       <c r="R20" t="n">
-        <v>7078711</v>
+        <v>7078270</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,11 +2647,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2653,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713631</v>
+        <v>119713697</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2693,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468508</v>
+        <v>468436</v>
       </c>
       <c r="R21" t="n">
-        <v>7078150</v>
+        <v>7079043</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,11 +2749,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2760,7 +2775,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713625</v>
+        <v>119713617</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2800,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468255</v>
+        <v>468290</v>
       </c>
       <c r="R22" t="n">
-        <v>7078014</v>
+        <v>7078881</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,7 +2855,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,7 +2882,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713634</v>
+        <v>119713646</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2907,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468498</v>
+        <v>468500</v>
       </c>
       <c r="R23" t="n">
-        <v>7078528</v>
+        <v>7078848</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,7 +2962,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,7 +2989,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713661</v>
+        <v>119713641</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3014,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468387</v>
+        <v>468546</v>
       </c>
       <c r="R24" t="n">
-        <v>7078948</v>
+        <v>7078889</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,7 +3096,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713640</v>
+        <v>119713639</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3121,10 +3136,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468538</v>
+        <v>468440</v>
       </c>
       <c r="R25" t="n">
-        <v>7078860</v>
+        <v>7078822</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3161,7 +3176,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3188,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713677</v>
+        <v>119713665</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,21 +3219,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468207</v>
+        <v>468309</v>
       </c>
       <c r="R26" t="n">
-        <v>7078579</v>
+        <v>7079036</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,6 +3279,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3290,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119713663</v>
+        <v>119713687</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3306,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3330,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468431</v>
+        <v>468461</v>
       </c>
       <c r="R27" t="n">
-        <v>7079071</v>
+        <v>7078992</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,11 +3386,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3397,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713666</v>
+        <v>119713685</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,21 +3428,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468267</v>
+        <v>468491</v>
       </c>
       <c r="R28" t="n">
-        <v>7079149</v>
+        <v>7078903</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3473,11 +3488,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3504,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713676</v>
+        <v>119713616</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3520,21 +3530,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,10 +3554,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468277</v>
+        <v>468263</v>
       </c>
       <c r="R29" t="n">
-        <v>7078898</v>
+        <v>7078968</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3580,6 +3590,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3606,7 +3621,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713626</v>
+        <v>119713657</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3646,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468396</v>
+        <v>468462</v>
       </c>
       <c r="R30" t="n">
-        <v>7078010</v>
+        <v>7078991</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,7 +3701,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3713,7 +3728,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713664</v>
+        <v>119713612</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3753,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468402</v>
+        <v>468171</v>
       </c>
       <c r="R31" t="n">
-        <v>7079059</v>
+        <v>7079106</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3793,7 +3808,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3820,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713612</v>
+        <v>119713704</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3836,21 +3851,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3860,10 +3875,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468171</v>
+        <v>468356</v>
       </c>
       <c r="R32" t="n">
-        <v>7079106</v>
+        <v>7077992</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3896,11 +3911,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3927,10 +3937,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713616</v>
+        <v>119713677</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,21 +3953,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3967,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468263</v>
+        <v>468207</v>
       </c>
       <c r="R33" t="n">
-        <v>7078968</v>
+        <v>7078579</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,11 +4013,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4034,7 +4039,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713652</v>
+        <v>119713664</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4074,10 +4079,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468431</v>
+        <v>468402</v>
       </c>
       <c r="R34" t="n">
-        <v>7078899</v>
+        <v>7079059</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4114,7 +4119,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4141,10 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713617</v>
+        <v>119713689</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4157,21 +4162,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4181,10 +4186,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>468290</v>
+        <v>468428</v>
       </c>
       <c r="R35" t="n">
-        <v>7078881</v>
+        <v>7078967</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4217,11 +4222,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4248,10 +4248,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119713667</v>
+        <v>119713609</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,21 +4264,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>468260</v>
+        <v>468506</v>
       </c>
       <c r="R36" t="n">
-        <v>7079151</v>
+        <v>7078126</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4324,11 +4324,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4355,7 +4350,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119713657</v>
+        <v>119713633</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4395,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>468462</v>
+        <v>468383</v>
       </c>
       <c r="R37" t="n">
-        <v>7078991</v>
+        <v>7078394</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4462,10 +4457,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119713680</v>
+        <v>119713638</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4478,21 +4473,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4502,10 +4497,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468356</v>
+        <v>468450</v>
       </c>
       <c r="R38" t="n">
-        <v>7078372</v>
+        <v>7078735</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4538,6 +4533,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4564,10 +4564,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119713708</v>
+        <v>119713695</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4580,21 +4580,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468354</v>
+        <v>468411</v>
       </c>
       <c r="R39" t="n">
-        <v>7078051</v>
+        <v>7078994</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4640,11 +4640,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4671,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119713647</v>
+        <v>119713705</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4687,21 +4682,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4711,10 +4706,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468481</v>
+        <v>468432</v>
       </c>
       <c r="R40" t="n">
-        <v>7078859</v>
+        <v>7078079</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,11 +4742,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4778,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119713662</v>
+        <v>119713691</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,21 +4784,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4818,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468406</v>
+        <v>468394</v>
       </c>
       <c r="R41" t="n">
-        <v>7078996</v>
+        <v>7078944</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4854,11 +4844,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4885,10 +4870,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119713641</v>
+        <v>119713681</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4901,21 +4886,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468546</v>
+        <v>468360</v>
       </c>
       <c r="R42" t="n">
-        <v>7078889</v>
+        <v>7078504</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4961,11 +4946,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4992,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119713693</v>
+        <v>119713623</v>
       </c>
       <c r="B43" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5008,21 +4988,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5032,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468379</v>
+        <v>468342</v>
       </c>
       <c r="R43" t="n">
-        <v>7078971</v>
+        <v>7078288</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5068,6 +5048,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5094,7 +5079,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119713643</v>
+        <v>119713637</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5134,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468546</v>
+        <v>468382</v>
       </c>
       <c r="R44" t="n">
-        <v>7078893</v>
+        <v>7078551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5308,7 +5293,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119713611</v>
+        <v>119713630</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5348,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468510</v>
+        <v>468507</v>
       </c>
       <c r="R46" t="n">
-        <v>7078916</v>
+        <v>7078135</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5388,7 +5373,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5415,7 +5400,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119713649</v>
+        <v>119713648</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5455,10 +5440,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468392</v>
+        <v>468397</v>
       </c>
       <c r="R47" t="n">
-        <v>7078891</v>
+        <v>7078890</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5495,7 +5480,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5522,7 +5507,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119713665</v>
+        <v>119713662</v>
       </c>
       <c r="B48" t="n">
         <v>57310</v>
@@ -5562,10 +5547,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468309</v>
+        <v>468406</v>
       </c>
       <c r="R48" t="n">
-        <v>7079036</v>
+        <v>7078996</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5602,7 +5587,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5629,10 +5614,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119713689</v>
+        <v>119713625</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5645,21 +5630,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5669,10 +5654,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468428</v>
+        <v>468255</v>
       </c>
       <c r="R49" t="n">
-        <v>7078967</v>
+        <v>7078014</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5705,6 +5690,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5731,10 +5721,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119713622</v>
+        <v>119713711</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5747,21 +5737,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5771,10 +5761,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468259</v>
+        <v>468242</v>
       </c>
       <c r="R50" t="n">
-        <v>7078432</v>
+        <v>7079178</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5811,7 +5801,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5838,7 +5828,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119713694</v>
+        <v>119713698</v>
       </c>
       <c r="B51" t="n">
         <v>79607</v>
@@ -5878,10 +5868,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468358</v>
+        <v>468338</v>
       </c>
       <c r="R51" t="n">
-        <v>7078970</v>
+        <v>7079023</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5940,7 +5930,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119713697</v>
+        <v>119713686</v>
       </c>
       <c r="B52" t="n">
         <v>79607</v>
@@ -5980,10 +5970,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468436</v>
+        <v>468414</v>
       </c>
       <c r="R52" t="n">
-        <v>7079043</v>
+        <v>7078890</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6042,10 +6032,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119713710</v>
+        <v>119713643</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6058,21 +6048,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6082,10 +6072,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468311</v>
+        <v>468546</v>
       </c>
       <c r="R53" t="n">
-        <v>7079041</v>
+        <v>7078893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6122,7 +6112,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6149,10 +6139,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119713707</v>
+        <v>119713614</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6165,21 +6155,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6189,10 +6179,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468344</v>
+        <v>468271</v>
       </c>
       <c r="R54" t="n">
-        <v>7078143</v>
+        <v>7079042</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6229,7 +6219,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6256,10 +6246,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119713675</v>
+        <v>119713635</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6272,21 +6262,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6296,10 +6286,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468269</v>
+        <v>468498</v>
       </c>
       <c r="R55" t="n">
-        <v>7078942</v>
+        <v>7078513</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6332,6 +6322,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6358,7 +6353,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119713635</v>
+        <v>119713622</v>
       </c>
       <c r="B56" t="n">
         <v>57310</v>
@@ -6398,10 +6393,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468498</v>
+        <v>468259</v>
       </c>
       <c r="R56" t="n">
-        <v>7078513</v>
+        <v>7078432</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6465,10 +6460,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119713629</v>
+        <v>119713678</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6481,21 +6476,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6505,10 +6500,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468444</v>
+        <v>468305</v>
       </c>
       <c r="R57" t="n">
-        <v>7078147</v>
+        <v>7078326</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6541,11 +6536,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6572,7 +6562,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119713638</v>
+        <v>119713632</v>
       </c>
       <c r="B58" t="n">
         <v>57310</v>
@@ -6612,10 +6602,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468450</v>
+        <v>468387</v>
       </c>
       <c r="R58" t="n">
-        <v>7078735</v>
+        <v>7078261</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6679,7 +6669,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119713650</v>
+        <v>119713620</v>
       </c>
       <c r="B59" t="n">
         <v>57310</v>
@@ -6719,10 +6709,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468408</v>
+        <v>468251</v>
       </c>
       <c r="R59" t="n">
-        <v>7078892</v>
+        <v>7078667</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6759,7 +6749,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6786,10 +6776,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119713636</v>
+        <v>119713707</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6802,21 +6792,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6826,10 +6816,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468454</v>
+        <v>468344</v>
       </c>
       <c r="R60" t="n">
-        <v>7078551</v>
+        <v>7078143</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6866,7 +6856,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6893,10 +6883,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119713706</v>
+        <v>119713683</v>
       </c>
       <c r="B61" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6909,21 +6899,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6933,10 +6923,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468414</v>
+        <v>468440</v>
       </c>
       <c r="R61" t="n">
-        <v>7078867</v>
+        <v>7078819</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6995,7 +6985,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119713684</v>
+        <v>119713692</v>
       </c>
       <c r="B62" t="n">
         <v>79607</v>
@@ -7035,10 +7025,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468525</v>
+        <v>468377</v>
       </c>
       <c r="R62" t="n">
-        <v>7078870</v>
+        <v>7078959</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7097,10 +7087,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119713692</v>
+        <v>119713660</v>
       </c>
       <c r="B63" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7113,21 +7103,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7137,10 +7127,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468377</v>
+        <v>468411</v>
       </c>
       <c r="R63" t="n">
-        <v>7078959</v>
+        <v>7078960</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7173,6 +7163,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7199,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119713628</v>
+        <v>119713684</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7215,21 +7210,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7239,10 +7234,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468442</v>
+        <v>468525</v>
       </c>
       <c r="R64" t="n">
-        <v>7078110</v>
+        <v>7078870</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7275,11 +7270,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7306,10 +7296,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119713627</v>
+        <v>119713610</v>
       </c>
       <c r="B65" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7322,21 +7312,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7346,10 +7336,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468420</v>
+        <v>468502</v>
       </c>
       <c r="R65" t="n">
-        <v>7078103</v>
+        <v>7078172</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7382,11 +7372,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7413,10 +7398,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119713691</v>
+        <v>119713666</v>
       </c>
       <c r="B66" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7429,21 +7414,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7453,10 +7438,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468394</v>
+        <v>468267</v>
       </c>
       <c r="R66" t="n">
-        <v>7078944</v>
+        <v>7079149</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7489,6 +7474,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7515,10 +7505,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119713698</v>
+        <v>119713611</v>
       </c>
       <c r="B67" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7531,21 +7521,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7555,10 +7545,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468338</v>
+        <v>468510</v>
       </c>
       <c r="R67" t="n">
-        <v>7079023</v>
+        <v>7078916</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7591,6 +7581,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7617,10 +7612,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119713678</v>
+        <v>119713654</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7633,21 +7628,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7657,10 +7652,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468305</v>
+        <v>468493</v>
       </c>
       <c r="R68" t="n">
-        <v>7078326</v>
+        <v>7078945</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7693,6 +7688,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7719,10 +7719,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119713685</v>
+        <v>119713627</v>
       </c>
       <c r="B69" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468491</v>
+        <v>468420</v>
       </c>
       <c r="R69" t="n">
-        <v>7078903</v>
+        <v>7078103</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7795,6 +7795,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7821,10 +7826,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119713711</v>
+        <v>119713624</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7837,21 +7842,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7861,10 +7866,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468242</v>
+        <v>468284</v>
       </c>
       <c r="R70" t="n">
-        <v>7079178</v>
+        <v>7078113</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7901,7 +7906,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7928,7 +7933,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119713639</v>
+        <v>119713618</v>
       </c>
       <c r="B71" t="n">
         <v>57310</v>
@@ -7968,10 +7973,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468440</v>
+        <v>468315</v>
       </c>
       <c r="R71" t="n">
-        <v>7078822</v>
+        <v>7078711</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8008,7 +8013,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8035,10 +8040,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119713613</v>
+        <v>119713708</v>
       </c>
       <c r="B72" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8051,21 +8056,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8075,10 +8080,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468269</v>
+        <v>468354</v>
       </c>
       <c r="R72" t="n">
-        <v>7079044</v>
+        <v>7078051</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8115,7 +8120,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8142,10 +8147,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119713709</v>
+        <v>119713694</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8158,21 +8163,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8182,10 +8187,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468530</v>
+        <v>468358</v>
       </c>
       <c r="R73" t="n">
-        <v>7078853</v>
+        <v>7078970</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8218,11 +8223,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8249,10 +8249,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119713704</v>
+        <v>119713680</v>
       </c>
       <c r="B74" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8265,21 +8265,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8292,7 +8292,7 @@
         <v>468356</v>
       </c>
       <c r="R74" t="n">
-        <v>7077992</v>
+        <v>7078372</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119713679</v>
+        <v>119713699</v>
       </c>
       <c r="B75" t="n">
         <v>79607</v>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468408</v>
+        <v>468287</v>
       </c>
       <c r="R75" t="n">
-        <v>7078270</v>
+        <v>7079069</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119713686</v>
+        <v>119713693</v>
       </c>
       <c r="B76" t="n">
         <v>79607</v>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468414</v>
+        <v>468379</v>
       </c>
       <c r="R76" t="n">
-        <v>7078890</v>
+        <v>7078971</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8555,10 +8555,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119713614</v>
+        <v>119713703</v>
       </c>
       <c r="B77" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8571,21 +8571,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8595,10 +8595,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468271</v>
+        <v>468369</v>
       </c>
       <c r="R77" t="n">
-        <v>7079042</v>
+        <v>7078973</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8631,11 +8631,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8662,7 +8657,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119713660</v>
+        <v>119713649</v>
       </c>
       <c r="B78" t="n">
         <v>57310</v>
@@ -8702,10 +8697,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468411</v>
+        <v>468392</v>
       </c>
       <c r="R78" t="n">
-        <v>7078960</v>
+        <v>7078891</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8742,7 +8737,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8769,7 +8764,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119713624</v>
+        <v>119713629</v>
       </c>
       <c r="B79" t="n">
         <v>57310</v>
@@ -8809,10 +8804,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468284</v>
+        <v>468444</v>
       </c>
       <c r="R79" t="n">
-        <v>7078113</v>
+        <v>7078147</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8849,7 +8844,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8876,10 +8871,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119713632</v>
+        <v>119713710</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8892,21 +8887,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8916,10 +8911,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468387</v>
+        <v>468311</v>
       </c>
       <c r="R80" t="n">
-        <v>7078261</v>
+        <v>7079041</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8956,7 +8951,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8983,10 +8978,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119713714</v>
+        <v>119713676</v>
       </c>
       <c r="B81" t="n">
-        <v>86878</v>
+        <v>79607</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8999,21 +8994,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9023,10 +9018,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468340</v>
+        <v>468277</v>
       </c>
       <c r="R81" t="n">
-        <v>7078142</v>
+        <v>7078898</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9085,10 +9080,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119713610</v>
+        <v>119713663</v>
       </c>
       <c r="B82" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9101,21 +9096,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9125,10 +9120,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468502</v>
+        <v>468431</v>
       </c>
       <c r="R82" t="n">
-        <v>7078172</v>
+        <v>7079071</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9161,6 +9156,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9187,7 +9187,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119713620</v>
+        <v>119713667</v>
       </c>
       <c r="B83" t="n">
         <v>57310</v>
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468251</v>
+        <v>468260</v>
       </c>
       <c r="R83" t="n">
-        <v>7078667</v>
+        <v>7079151</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9294,7 +9294,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119713648</v>
+        <v>119713640</v>
       </c>
       <c r="B84" t="n">
         <v>57310</v>
@@ -9334,10 +9334,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468397</v>
+        <v>468538</v>
       </c>
       <c r="R84" t="n">
-        <v>7078890</v>
+        <v>7078860</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119713684</v>
+        <v>119713610</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7210,21 +7210,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7234,10 +7234,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468525</v>
+        <v>468502</v>
       </c>
       <c r="R64" t="n">
-        <v>7078870</v>
+        <v>7078172</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7296,10 +7296,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119713610</v>
+        <v>119713684</v>
       </c>
       <c r="B65" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7312,21 +7312,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468502</v>
+        <v>468525</v>
       </c>
       <c r="R65" t="n">
-        <v>7078172</v>
+        <v>7078870</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8871,10 +8871,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119713710</v>
+        <v>119713676</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8887,21 +8887,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468311</v>
+        <v>468277</v>
       </c>
       <c r="R80" t="n">
-        <v>7079041</v>
+        <v>7078898</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8947,11 +8947,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8978,10 +8973,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119713676</v>
+        <v>119713710</v>
       </c>
       <c r="B81" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8994,21 +8989,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9018,10 +9013,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468277</v>
+        <v>468311</v>
       </c>
       <c r="R81" t="n">
-        <v>7078898</v>
+        <v>7079041</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9054,6 +9049,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713636</v>
+        <v>119713686</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468454</v>
+        <v>468414</v>
       </c>
       <c r="R2" t="n">
-        <v>7078551</v>
+        <v>7078890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713647</v>
+        <v>119713708</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468481</v>
+        <v>468354</v>
       </c>
       <c r="R3" t="n">
-        <v>7078859</v>
+        <v>7078051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713645</v>
+        <v>119713706</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468491</v>
+        <v>468414</v>
       </c>
       <c r="R4" t="n">
-        <v>7078873</v>
+        <v>7078867</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713613</v>
+        <v>119713665</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468269</v>
+        <v>468309</v>
       </c>
       <c r="R5" t="n">
-        <v>7079044</v>
+        <v>7079036</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713634</v>
+        <v>119713652</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468498</v>
+        <v>468431</v>
       </c>
       <c r="R6" t="n">
-        <v>7078528</v>
+        <v>7078899</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713709</v>
+        <v>119713633</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468530</v>
+        <v>468383</v>
       </c>
       <c r="R7" t="n">
-        <v>7078853</v>
+        <v>7078394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713714</v>
+        <v>119713643</v>
       </c>
       <c r="B8" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468340</v>
+        <v>468546</v>
       </c>
       <c r="R8" t="n">
-        <v>7078142</v>
+        <v>7078893</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713712</v>
+        <v>119713663</v>
       </c>
       <c r="B9" t="n">
-        <v>91128</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468491</v>
+        <v>468431</v>
       </c>
       <c r="R9" t="n">
-        <v>7078902</v>
+        <v>7079071</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713628</v>
+        <v>119713682</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468442</v>
+        <v>468392</v>
       </c>
       <c r="R10" t="n">
-        <v>7078110</v>
+        <v>7078534</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713652</v>
+        <v>119713695</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468431</v>
+        <v>468411</v>
       </c>
       <c r="R11" t="n">
-        <v>7078899</v>
+        <v>7078994</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713673</v>
+        <v>119713707</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468436</v>
+        <v>468344</v>
       </c>
       <c r="R12" t="n">
-        <v>7079043</v>
+        <v>7078143</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713682</v>
+        <v>119713613</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468392</v>
+        <v>468269</v>
       </c>
       <c r="R13" t="n">
-        <v>7078534</v>
+        <v>7079044</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713675</v>
+        <v>119713681</v>
       </c>
       <c r="B14" t="n">
         <v>79607</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468269</v>
+        <v>468360</v>
       </c>
       <c r="R14" t="n">
-        <v>7078942</v>
+        <v>7078504</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713706</v>
+        <v>119713710</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468414</v>
+        <v>468311</v>
       </c>
       <c r="R15" t="n">
-        <v>7078867</v>
+        <v>7079041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,6 +2117,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713626</v>
+        <v>119713641</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2183,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468396</v>
+        <v>468546</v>
       </c>
       <c r="R16" t="n">
-        <v>7078010</v>
+        <v>7078889</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713650</v>
+        <v>119713677</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468408</v>
+        <v>468207</v>
       </c>
       <c r="R17" t="n">
-        <v>7078892</v>
+        <v>7078579</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713631</v>
+        <v>119713648</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468508</v>
+        <v>468397</v>
       </c>
       <c r="R18" t="n">
-        <v>7078150</v>
+        <v>7078890</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713661</v>
+        <v>119713609</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468387</v>
+        <v>468506</v>
       </c>
       <c r="R19" t="n">
-        <v>7078948</v>
+        <v>7078126</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,11 +2540,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,7 +2566,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713679</v>
+        <v>119713685</v>
       </c>
       <c r="B20" t="n">
         <v>79607</v>
@@ -2611,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468408</v>
+        <v>468491</v>
       </c>
       <c r="R20" t="n">
-        <v>7078270</v>
+        <v>7078903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,7 +2668,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713697</v>
+        <v>119713684</v>
       </c>
       <c r="B21" t="n">
         <v>79607</v>
@@ -2713,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468436</v>
+        <v>468525</v>
       </c>
       <c r="R21" t="n">
-        <v>7079043</v>
+        <v>7078870</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,7 +2770,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713617</v>
+        <v>119713650</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2815,10 +2810,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468290</v>
+        <v>468408</v>
       </c>
       <c r="R22" t="n">
-        <v>7078881</v>
+        <v>7078892</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,7 +2850,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,7 +2877,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713646</v>
+        <v>119713618</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468500</v>
+        <v>468315</v>
       </c>
       <c r="R23" t="n">
-        <v>7078848</v>
+        <v>7078711</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2962,7 +2957,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2989,7 +2984,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713641</v>
+        <v>119713625</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3029,10 +3024,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468546</v>
+        <v>468255</v>
       </c>
       <c r="R24" t="n">
-        <v>7078889</v>
+        <v>7078014</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713639</v>
+        <v>119713676</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3112,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3136,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468440</v>
+        <v>468277</v>
       </c>
       <c r="R25" t="n">
-        <v>7078822</v>
+        <v>7078898</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3172,11 +3167,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713665</v>
+        <v>119713705</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,21 +3209,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3243,10 +3233,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468309</v>
+        <v>468432</v>
       </c>
       <c r="R26" t="n">
-        <v>7079036</v>
+        <v>7078079</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3279,11 +3269,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3310,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119713687</v>
+        <v>119713626</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468461</v>
+        <v>468396</v>
       </c>
       <c r="R27" t="n">
-        <v>7078992</v>
+        <v>7078010</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,6 +3371,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3412,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713685</v>
+        <v>119713657</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3428,21 +3418,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468491</v>
+        <v>468462</v>
       </c>
       <c r="R28" t="n">
-        <v>7078903</v>
+        <v>7078991</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,6 +3478,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,7 +3509,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713616</v>
+        <v>119713620</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3554,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468263</v>
+        <v>468251</v>
       </c>
       <c r="R29" t="n">
-        <v>7078968</v>
+        <v>7078667</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3594,7 +3589,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,7 +3616,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713657</v>
+        <v>119713628</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3661,10 +3656,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468462</v>
+        <v>468442</v>
       </c>
       <c r="R30" t="n">
-        <v>7078991</v>
+        <v>7078110</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,7 +3723,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713612</v>
+        <v>119713638</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468171</v>
+        <v>468450</v>
       </c>
       <c r="R31" t="n">
-        <v>7079106</v>
+        <v>7078735</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,7 +3803,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3835,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713704</v>
+        <v>119713612</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,21 +3846,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3875,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468356</v>
+        <v>468171</v>
       </c>
       <c r="R32" t="n">
-        <v>7077992</v>
+        <v>7079106</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3911,6 +3906,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3937,10 +3937,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713677</v>
+        <v>119713617</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3953,21 +3953,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468207</v>
+        <v>468290</v>
       </c>
       <c r="R33" t="n">
-        <v>7078579</v>
+        <v>7078881</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,6 +4013,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4039,7 +4044,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713664</v>
+        <v>119713647</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4079,10 +4084,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468402</v>
+        <v>468481</v>
       </c>
       <c r="R34" t="n">
-        <v>7079059</v>
+        <v>7078859</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4119,7 +4124,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4146,10 +4151,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713689</v>
+        <v>119713666</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4162,21 +4167,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4186,10 +4191,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>468428</v>
+        <v>468267</v>
       </c>
       <c r="R35" t="n">
-        <v>7078967</v>
+        <v>7079149</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4222,6 +4227,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4248,10 +4258,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119713609</v>
+        <v>119713631</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,21 +4274,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4288,10 +4298,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>468506</v>
+        <v>468508</v>
       </c>
       <c r="R36" t="n">
-        <v>7078126</v>
+        <v>7078150</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4324,6 +4334,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,10 +4365,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119713633</v>
+        <v>119713610</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,21 +4381,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4390,10 +4405,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>468383</v>
+        <v>468502</v>
       </c>
       <c r="R37" t="n">
-        <v>7078394</v>
+        <v>7078172</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4426,11 +4441,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4457,10 +4467,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119713638</v>
+        <v>119713680</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4473,21 +4483,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4497,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468450</v>
+        <v>468356</v>
       </c>
       <c r="R38" t="n">
-        <v>7078735</v>
+        <v>7078372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4533,11 +4543,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4564,7 +4569,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119713695</v>
+        <v>119713693</v>
       </c>
       <c r="B39" t="n">
         <v>79607</v>
@@ -4604,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468411</v>
+        <v>468379</v>
       </c>
       <c r="R39" t="n">
-        <v>7078994</v>
+        <v>7078971</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119713705</v>
+        <v>119713692</v>
       </c>
       <c r="B40" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4682,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4706,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468432</v>
+        <v>468377</v>
       </c>
       <c r="R40" t="n">
-        <v>7078079</v>
+        <v>7078959</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4768,7 +4773,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119713691</v>
+        <v>119713694</v>
       </c>
       <c r="B41" t="n">
         <v>79607</v>
@@ -4808,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468394</v>
+        <v>468358</v>
       </c>
       <c r="R41" t="n">
-        <v>7078944</v>
+        <v>7078970</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119713681</v>
+        <v>119713709</v>
       </c>
       <c r="B42" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,21 +4891,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4910,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468360</v>
+        <v>468530</v>
       </c>
       <c r="R42" t="n">
-        <v>7078504</v>
+        <v>7078853</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4946,6 +4951,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4972,7 +4982,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119713623</v>
+        <v>119713639</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5012,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468342</v>
+        <v>468440</v>
       </c>
       <c r="R43" t="n">
-        <v>7078288</v>
+        <v>7078822</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5052,7 +5062,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5079,7 +5089,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119713637</v>
+        <v>119713629</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5119,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468382</v>
+        <v>468444</v>
       </c>
       <c r="R44" t="n">
-        <v>7078551</v>
+        <v>7078147</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,7 +5169,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5186,10 +5196,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119713621</v>
+        <v>119713712</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>91128</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5198,25 +5208,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5226,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468270</v>
+        <v>468491</v>
       </c>
       <c r="R45" t="n">
-        <v>7078423</v>
+        <v>7078902</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5262,11 +5272,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,7 +5298,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119713630</v>
+        <v>119713623</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5333,10 +5338,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468507</v>
+        <v>468342</v>
       </c>
       <c r="R46" t="n">
-        <v>7078135</v>
+        <v>7078288</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5400,7 +5405,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119713648</v>
+        <v>119713636</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5440,10 +5445,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468397</v>
+        <v>468454</v>
       </c>
       <c r="R47" t="n">
-        <v>7078890</v>
+        <v>7078551</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5480,7 +5485,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5507,7 +5512,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119713662</v>
+        <v>119713630</v>
       </c>
       <c r="B48" t="n">
         <v>57310</v>
@@ -5547,10 +5552,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468406</v>
+        <v>468507</v>
       </c>
       <c r="R48" t="n">
-        <v>7078996</v>
+        <v>7078135</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5614,7 +5619,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119713625</v>
+        <v>119713645</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5654,10 +5659,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468255</v>
+        <v>468491</v>
       </c>
       <c r="R49" t="n">
-        <v>7078014</v>
+        <v>7078873</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5694,7 +5699,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5721,10 +5726,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119713711</v>
+        <v>119713664</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5737,21 +5742,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5761,10 +5766,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468242</v>
+        <v>468402</v>
       </c>
       <c r="R50" t="n">
-        <v>7079178</v>
+        <v>7079059</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5801,7 +5806,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5828,10 +5833,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119713698</v>
+        <v>119713660</v>
       </c>
       <c r="B51" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5844,21 +5849,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5868,10 +5873,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468338</v>
+        <v>468411</v>
       </c>
       <c r="R51" t="n">
-        <v>7079023</v>
+        <v>7078960</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5904,6 +5909,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5930,10 +5940,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119713686</v>
+        <v>119713624</v>
       </c>
       <c r="B52" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5946,21 +5956,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5970,10 +5980,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468414</v>
+        <v>468284</v>
       </c>
       <c r="R52" t="n">
-        <v>7078890</v>
+        <v>7078113</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6006,6 +6016,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6032,7 +6047,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119713643</v>
+        <v>119713622</v>
       </c>
       <c r="B53" t="n">
         <v>57310</v>
@@ -6072,10 +6087,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468546</v>
+        <v>468259</v>
       </c>
       <c r="R53" t="n">
-        <v>7078893</v>
+        <v>7078432</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6139,10 +6154,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119713614</v>
+        <v>119713675</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6155,21 +6170,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6179,10 +6194,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468271</v>
+        <v>468269</v>
       </c>
       <c r="R54" t="n">
-        <v>7079042</v>
+        <v>7078942</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6215,11 +6230,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6246,10 +6256,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119713635</v>
+        <v>119713691</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6262,21 +6272,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6286,10 +6296,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468498</v>
+        <v>468394</v>
       </c>
       <c r="R55" t="n">
-        <v>7078513</v>
+        <v>7078944</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6322,11 +6332,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6353,7 +6358,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119713622</v>
+        <v>119713632</v>
       </c>
       <c r="B56" t="n">
         <v>57310</v>
@@ -6393,10 +6398,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468259</v>
+        <v>468387</v>
       </c>
       <c r="R56" t="n">
-        <v>7078432</v>
+        <v>7078261</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6460,10 +6465,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119713678</v>
+        <v>119713640</v>
       </c>
       <c r="B57" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6476,21 +6481,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6500,10 +6505,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468305</v>
+        <v>468538</v>
       </c>
       <c r="R57" t="n">
-        <v>7078326</v>
+        <v>7078860</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6536,6 +6541,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6562,10 +6572,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119713632</v>
+        <v>119713673</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6578,21 +6588,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6602,10 +6612,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468387</v>
+        <v>468436</v>
       </c>
       <c r="R58" t="n">
-        <v>7078261</v>
+        <v>7079043</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6638,11 +6648,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6669,10 +6674,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119713620</v>
+        <v>119713703</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6685,21 +6690,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6709,10 +6714,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468251</v>
+        <v>468369</v>
       </c>
       <c r="R59" t="n">
-        <v>7078667</v>
+        <v>7078973</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6745,11 +6750,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6776,10 +6776,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119713707</v>
+        <v>119713683</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468344</v>
+        <v>468440</v>
       </c>
       <c r="R60" t="n">
-        <v>7078143</v>
+        <v>7078819</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6852,11 +6852,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6883,7 +6878,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119713683</v>
+        <v>119713697</v>
       </c>
       <c r="B61" t="n">
         <v>79607</v>
@@ -6923,10 +6918,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468440</v>
+        <v>468436</v>
       </c>
       <c r="R61" t="n">
-        <v>7078819</v>
+        <v>7079043</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6985,10 +6980,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119713692</v>
+        <v>119713616</v>
       </c>
       <c r="B62" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7001,21 +6996,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7025,10 +7020,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468377</v>
+        <v>468263</v>
       </c>
       <c r="R62" t="n">
-        <v>7078959</v>
+        <v>7078968</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7061,6 +7056,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7087,7 +7087,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119713660</v>
+        <v>119713646</v>
       </c>
       <c r="B63" t="n">
         <v>57310</v>
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468411</v>
+        <v>468500</v>
       </c>
       <c r="R63" t="n">
-        <v>7078960</v>
+        <v>7078848</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119713610</v>
+        <v>119713621</v>
       </c>
       <c r="B64" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7210,21 +7210,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7234,10 +7234,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468502</v>
+        <v>468270</v>
       </c>
       <c r="R64" t="n">
-        <v>7078172</v>
+        <v>7078423</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7270,6 +7270,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7296,7 +7301,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119713684</v>
+        <v>119713699</v>
       </c>
       <c r="B65" t="n">
         <v>79607</v>
@@ -7336,10 +7341,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468525</v>
+        <v>468287</v>
       </c>
       <c r="R65" t="n">
-        <v>7078870</v>
+        <v>7079069</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7398,10 +7403,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119713666</v>
+        <v>119713714</v>
       </c>
       <c r="B66" t="n">
-        <v>57310</v>
+        <v>86878</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7414,21 +7419,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7438,10 +7443,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468267</v>
+        <v>468340</v>
       </c>
       <c r="R66" t="n">
-        <v>7079149</v>
+        <v>7078142</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7474,11 +7479,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7505,10 +7505,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119713611</v>
+        <v>119713711</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7521,21 +7521,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468510</v>
+        <v>468242</v>
       </c>
       <c r="R67" t="n">
-        <v>7078916</v>
+        <v>7079178</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7612,10 +7612,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119713654</v>
+        <v>119713678</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7628,21 +7628,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7652,10 +7652,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468493</v>
+        <v>468305</v>
       </c>
       <c r="R68" t="n">
-        <v>7078945</v>
+        <v>7078326</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7688,11 +7688,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7719,7 +7714,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119713627</v>
+        <v>119713637</v>
       </c>
       <c r="B69" t="n">
         <v>57310</v>
@@ -7759,10 +7754,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468420</v>
+        <v>468382</v>
       </c>
       <c r="R69" t="n">
-        <v>7078103</v>
+        <v>7078551</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7826,7 +7821,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119713624</v>
+        <v>119713614</v>
       </c>
       <c r="B70" t="n">
         <v>57310</v>
@@ -7866,10 +7861,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468284</v>
+        <v>468271</v>
       </c>
       <c r="R70" t="n">
-        <v>7078113</v>
+        <v>7079042</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7906,7 +7901,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7933,7 +7928,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119713618</v>
+        <v>119713611</v>
       </c>
       <c r="B71" t="n">
         <v>57310</v>
@@ -7973,10 +7968,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468315</v>
+        <v>468510</v>
       </c>
       <c r="R71" t="n">
-        <v>7078711</v>
+        <v>7078916</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8013,7 +8008,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8040,10 +8035,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119713708</v>
+        <v>119713634</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8056,21 +8051,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8080,10 +8075,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468354</v>
+        <v>468498</v>
       </c>
       <c r="R72" t="n">
-        <v>7078051</v>
+        <v>7078528</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8120,7 +8115,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8147,7 +8142,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119713694</v>
+        <v>119713687</v>
       </c>
       <c r="B73" t="n">
         <v>79607</v>
@@ -8187,10 +8182,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468358</v>
+        <v>468461</v>
       </c>
       <c r="R73" t="n">
-        <v>7078970</v>
+        <v>7078992</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8249,10 +8244,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119713680</v>
+        <v>119713704</v>
       </c>
       <c r="B74" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8265,21 +8260,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8292,7 +8287,7 @@
         <v>468356</v>
       </c>
       <c r="R74" t="n">
-        <v>7078372</v>
+        <v>7077992</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8351,10 +8346,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119713699</v>
+        <v>119713654</v>
       </c>
       <c r="B75" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8367,21 +8362,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8391,10 +8386,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468287</v>
+        <v>468493</v>
       </c>
       <c r="R75" t="n">
-        <v>7079069</v>
+        <v>7078945</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8427,6 +8422,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8453,10 +8453,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119713693</v>
+        <v>119713661</v>
       </c>
       <c r="B76" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8469,21 +8469,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468379</v>
+        <v>468387</v>
       </c>
       <c r="R76" t="n">
-        <v>7078971</v>
+        <v>7078948</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,6 +8529,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8555,10 +8560,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119713703</v>
+        <v>119713689</v>
       </c>
       <c r="B77" t="n">
-        <v>90558</v>
+        <v>79607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8571,21 +8576,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8595,10 +8600,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468369</v>
+        <v>468428</v>
       </c>
       <c r="R77" t="n">
-        <v>7078973</v>
+        <v>7078967</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8657,10 +8662,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119713649</v>
+        <v>119713679</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8673,21 +8678,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8697,10 +8702,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468392</v>
+        <v>468408</v>
       </c>
       <c r="R78" t="n">
-        <v>7078891</v>
+        <v>7078270</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8733,11 +8738,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8764,10 +8764,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119713629</v>
+        <v>119713698</v>
       </c>
       <c r="B79" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8780,21 +8780,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468444</v>
+        <v>468338</v>
       </c>
       <c r="R79" t="n">
-        <v>7078147</v>
+        <v>7079023</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8840,11 +8840,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8871,10 +8866,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119713676</v>
+        <v>119713649</v>
       </c>
       <c r="B80" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8887,21 +8882,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8911,10 +8906,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468277</v>
+        <v>468392</v>
       </c>
       <c r="R80" t="n">
-        <v>7078898</v>
+        <v>7078891</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8947,6 +8942,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8973,10 +8973,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119713710</v>
+        <v>119713667</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8989,21 +8989,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9013,10 +9013,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468311</v>
+        <v>468260</v>
       </c>
       <c r="R81" t="n">
-        <v>7079041</v>
+        <v>7079151</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9080,7 +9080,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119713663</v>
+        <v>119713627</v>
       </c>
       <c r="B82" t="n">
         <v>57310</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468431</v>
+        <v>468420</v>
       </c>
       <c r="R82" t="n">
-        <v>7079071</v>
+        <v>7078103</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9187,7 +9187,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119713667</v>
+        <v>119713635</v>
       </c>
       <c r="B83" t="n">
         <v>57310</v>
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468260</v>
+        <v>468498</v>
       </c>
       <c r="R83" t="n">
-        <v>7079151</v>
+        <v>7078513</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9294,7 +9294,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119713640</v>
+        <v>119713662</v>
       </c>
       <c r="B84" t="n">
         <v>57310</v>
@@ -9334,10 +9334,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468538</v>
+        <v>468406</v>
       </c>
       <c r="R84" t="n">
-        <v>7078860</v>
+        <v>7078996</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713710</v>
+        <v>119713641</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468311</v>
+        <v>468546</v>
       </c>
       <c r="R15" t="n">
-        <v>7079041</v>
+        <v>7078889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713641</v>
+        <v>119713710</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468546</v>
+        <v>468311</v>
       </c>
       <c r="R16" t="n">
-        <v>7078889</v>
+        <v>7079041</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -7612,10 +7612,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119713678</v>
+        <v>119713637</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7628,21 +7628,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7652,10 +7652,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468305</v>
+        <v>468382</v>
       </c>
       <c r="R68" t="n">
-        <v>7078326</v>
+        <v>7078551</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7688,6 +7688,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7714,7 +7719,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119713637</v>
+        <v>119713614</v>
       </c>
       <c r="B69" t="n">
         <v>57310</v>
@@ -7754,10 +7759,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468382</v>
+        <v>468271</v>
       </c>
       <c r="R69" t="n">
-        <v>7078551</v>
+        <v>7079042</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7794,7 +7799,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7821,7 +7826,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119713614</v>
+        <v>119713611</v>
       </c>
       <c r="B70" t="n">
         <v>57310</v>
@@ -7861,10 +7866,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468271</v>
+        <v>468510</v>
       </c>
       <c r="R70" t="n">
-        <v>7079042</v>
+        <v>7078916</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7901,7 +7906,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7928,7 +7933,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119713611</v>
+        <v>119713634</v>
       </c>
       <c r="B71" t="n">
         <v>57310</v>
@@ -7968,10 +7973,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468510</v>
+        <v>468498</v>
       </c>
       <c r="R71" t="n">
-        <v>7078916</v>
+        <v>7078528</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8008,7 +8013,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8035,10 +8040,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119713634</v>
+        <v>119713678</v>
       </c>
       <c r="B72" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8051,21 +8056,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8075,10 +8080,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468498</v>
+        <v>468305</v>
       </c>
       <c r="R72" t="n">
-        <v>7078528</v>
+        <v>7078326</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8111,11 +8116,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8142,10 +8142,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119713687</v>
+        <v>119713704</v>
       </c>
       <c r="B73" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8158,21 +8158,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468461</v>
+        <v>468356</v>
       </c>
       <c r="R73" t="n">
-        <v>7078992</v>
+        <v>7077992</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119713704</v>
+        <v>119713654</v>
       </c>
       <c r="B74" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8260,21 +8260,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468356</v>
+        <v>468493</v>
       </c>
       <c r="R74" t="n">
-        <v>7077992</v>
+        <v>7078945</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8320,6 +8320,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8346,7 +8351,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119713654</v>
+        <v>119713661</v>
       </c>
       <c r="B75" t="n">
         <v>57310</v>
@@ -8386,10 +8391,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468493</v>
+        <v>468387</v>
       </c>
       <c r="R75" t="n">
-        <v>7078945</v>
+        <v>7078948</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8453,10 +8458,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119713661</v>
+        <v>119713687</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8469,21 +8474,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8493,10 +8498,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468387</v>
+        <v>468461</v>
       </c>
       <c r="R76" t="n">
-        <v>7078948</v>
+        <v>7078992</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,11 +8534,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8560,10 +8560,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119713689</v>
+        <v>119713649</v>
       </c>
       <c r="B77" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8576,21 +8576,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468428</v>
+        <v>468392</v>
       </c>
       <c r="R77" t="n">
-        <v>7078967</v>
+        <v>7078891</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,6 +8636,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8662,10 +8667,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119713679</v>
+        <v>119713667</v>
       </c>
       <c r="B78" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8678,21 +8683,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8702,10 +8707,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468408</v>
+        <v>468260</v>
       </c>
       <c r="R78" t="n">
-        <v>7078270</v>
+        <v>7079151</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8738,6 +8743,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8764,7 +8774,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119713698</v>
+        <v>119713689</v>
       </c>
       <c r="B79" t="n">
         <v>79607</v>
@@ -8804,10 +8814,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468338</v>
+        <v>468428</v>
       </c>
       <c r="R79" t="n">
-        <v>7079023</v>
+        <v>7078967</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8866,10 +8876,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119713649</v>
+        <v>119713679</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8882,21 +8892,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8906,10 +8916,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468392</v>
+        <v>468408</v>
       </c>
       <c r="R80" t="n">
-        <v>7078891</v>
+        <v>7078270</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8942,11 +8952,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8973,10 +8978,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119713667</v>
+        <v>119713698</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8989,21 +8994,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9013,10 +9018,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468260</v>
+        <v>468338</v>
       </c>
       <c r="R81" t="n">
-        <v>7079151</v>
+        <v>7079023</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9049,11 +9054,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -8142,10 +8142,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119713704</v>
+        <v>119713687</v>
       </c>
       <c r="B73" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8158,21 +8158,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468356</v>
+        <v>468461</v>
       </c>
       <c r="R73" t="n">
-        <v>7077992</v>
+        <v>7078992</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119713654</v>
+        <v>119713704</v>
       </c>
       <c r="B74" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8260,21 +8260,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468493</v>
+        <v>468356</v>
       </c>
       <c r="R74" t="n">
-        <v>7078945</v>
+        <v>7077992</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8320,11 +8320,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8351,7 +8346,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119713661</v>
+        <v>119713654</v>
       </c>
       <c r="B75" t="n">
         <v>57310</v>
@@ -8391,10 +8386,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468387</v>
+        <v>468493</v>
       </c>
       <c r="R75" t="n">
-        <v>7078948</v>
+        <v>7078945</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8458,10 +8453,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119713687</v>
+        <v>119713661</v>
       </c>
       <c r="B76" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8474,21 +8469,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8498,10 +8493,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468461</v>
+        <v>468387</v>
       </c>
       <c r="R76" t="n">
-        <v>7078992</v>
+        <v>7078948</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8534,6 +8529,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8560,10 +8560,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119713649</v>
+        <v>119713689</v>
       </c>
       <c r="B77" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8576,21 +8576,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468392</v>
+        <v>468428</v>
       </c>
       <c r="R77" t="n">
-        <v>7078891</v>
+        <v>7078967</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,11 +8636,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8667,10 +8662,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119713667</v>
+        <v>119713679</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8683,21 +8678,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8707,10 +8702,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468260</v>
+        <v>468408</v>
       </c>
       <c r="R78" t="n">
-        <v>7079151</v>
+        <v>7078270</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8743,11 +8738,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8774,7 +8764,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119713689</v>
+        <v>119713698</v>
       </c>
       <c r="B79" t="n">
         <v>79607</v>
@@ -8814,10 +8804,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468428</v>
+        <v>468338</v>
       </c>
       <c r="R79" t="n">
-        <v>7078967</v>
+        <v>7079023</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8876,10 +8866,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119713679</v>
+        <v>119713649</v>
       </c>
       <c r="B80" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8892,21 +8882,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8916,10 +8906,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468408</v>
+        <v>468392</v>
       </c>
       <c r="R80" t="n">
-        <v>7078270</v>
+        <v>7078891</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8952,6 +8942,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8978,10 +8973,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119713698</v>
+        <v>119713667</v>
       </c>
       <c r="B81" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8994,21 +8989,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9018,10 +9013,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468338</v>
+        <v>468260</v>
       </c>
       <c r="R81" t="n">
-        <v>7079023</v>
+        <v>7079151</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9054,6 +9049,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713641</v>
+        <v>119713710</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468546</v>
+        <v>468311</v>
       </c>
       <c r="R15" t="n">
-        <v>7078889</v>
+        <v>7079041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713710</v>
+        <v>119713641</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468311</v>
+        <v>468546</v>
       </c>
       <c r="R16" t="n">
-        <v>7079041</v>
+        <v>7078889</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2668,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713684</v>
+        <v>119713650</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468525</v>
+        <v>468408</v>
       </c>
       <c r="R21" t="n">
-        <v>7078870</v>
+        <v>7078892</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,6 +2744,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2770,7 +2775,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713650</v>
+        <v>119713618</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2810,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468408</v>
+        <v>468315</v>
       </c>
       <c r="R22" t="n">
-        <v>7078892</v>
+        <v>7078711</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713618</v>
+        <v>119713684</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468315</v>
+        <v>468525</v>
       </c>
       <c r="R23" t="n">
-        <v>7078711</v>
+        <v>7078870</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,11 +2958,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -8142,10 +8142,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119713687</v>
+        <v>119713704</v>
       </c>
       <c r="B73" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8158,21 +8158,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468461</v>
+        <v>468356</v>
       </c>
       <c r="R73" t="n">
-        <v>7078992</v>
+        <v>7077992</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119713704</v>
+        <v>119713654</v>
       </c>
       <c r="B74" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8260,21 +8260,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468356</v>
+        <v>468493</v>
       </c>
       <c r="R74" t="n">
-        <v>7077992</v>
+        <v>7078945</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8320,6 +8320,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8346,7 +8351,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119713654</v>
+        <v>119713661</v>
       </c>
       <c r="B75" t="n">
         <v>57310</v>
@@ -8386,10 +8391,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468493</v>
+        <v>468387</v>
       </c>
       <c r="R75" t="n">
-        <v>7078945</v>
+        <v>7078948</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8453,10 +8458,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119713661</v>
+        <v>119713687</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8469,21 +8474,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8493,10 +8498,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468387</v>
+        <v>468461</v>
       </c>
       <c r="R76" t="n">
-        <v>7078948</v>
+        <v>7078992</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,11 +8534,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713695</v>
+        <v>119713707</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468411</v>
+        <v>468344</v>
       </c>
       <c r="R11" t="n">
-        <v>7078994</v>
+        <v>7078143</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713707</v>
+        <v>119713695</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468344</v>
+        <v>468411</v>
       </c>
       <c r="R12" t="n">
-        <v>7078143</v>
+        <v>7078994</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713710</v>
+        <v>119713641</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468311</v>
+        <v>468546</v>
       </c>
       <c r="R15" t="n">
-        <v>7079041</v>
+        <v>7078889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713641</v>
+        <v>119713710</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468546</v>
+        <v>468311</v>
       </c>
       <c r="R16" t="n">
-        <v>7078889</v>
+        <v>7079041</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3091,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713676</v>
+        <v>119713705</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468277</v>
+        <v>468432</v>
       </c>
       <c r="R25" t="n">
-        <v>7078898</v>
+        <v>7078079</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713705</v>
+        <v>119713676</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,21 +3209,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468432</v>
+        <v>468277</v>
       </c>
       <c r="R26" t="n">
-        <v>7078079</v>
+        <v>7078898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -6572,10 +6572,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119713673</v>
+        <v>119713683</v>
       </c>
       <c r="B58" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6588,21 +6588,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468436</v>
+        <v>468440</v>
       </c>
       <c r="R58" t="n">
-        <v>7079043</v>
+        <v>7078819</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6674,10 +6674,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119713703</v>
+        <v>119713697</v>
       </c>
       <c r="B59" t="n">
-        <v>90558</v>
+        <v>79607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6690,21 +6690,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468369</v>
+        <v>468436</v>
       </c>
       <c r="R59" t="n">
-        <v>7078973</v>
+        <v>7079043</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6776,10 +6776,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119713683</v>
+        <v>119713616</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468440</v>
+        <v>468263</v>
       </c>
       <c r="R60" t="n">
-        <v>7078819</v>
+        <v>7078968</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6852,6 +6852,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6878,10 +6883,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119713697</v>
+        <v>119713646</v>
       </c>
       <c r="B61" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6894,21 +6899,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6918,10 +6923,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468436</v>
+        <v>468500</v>
       </c>
       <c r="R61" t="n">
-        <v>7079043</v>
+        <v>7078848</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6954,6 +6959,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6980,7 +6990,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119713616</v>
+        <v>119713621</v>
       </c>
       <c r="B62" t="n">
         <v>57310</v>
@@ -7020,10 +7030,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468263</v>
+        <v>468270</v>
       </c>
       <c r="R62" t="n">
-        <v>7078968</v>
+        <v>7078423</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7060,7 +7070,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7087,10 +7097,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119713646</v>
+        <v>119713673</v>
       </c>
       <c r="B63" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7103,21 +7113,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7127,10 +7137,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468500</v>
+        <v>468436</v>
       </c>
       <c r="R63" t="n">
-        <v>7078848</v>
+        <v>7079043</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7163,11 +7173,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7194,10 +7199,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119713621</v>
+        <v>119713703</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7210,21 +7215,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7234,10 +7239,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468270</v>
+        <v>468369</v>
       </c>
       <c r="R64" t="n">
-        <v>7078423</v>
+        <v>7078973</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7270,11 +7275,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8142,10 +8142,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119713704</v>
+        <v>119713687</v>
       </c>
       <c r="B73" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8158,21 +8158,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468356</v>
+        <v>468461</v>
       </c>
       <c r="R73" t="n">
-        <v>7077992</v>
+        <v>7078992</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119713654</v>
+        <v>119713704</v>
       </c>
       <c r="B74" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8260,21 +8260,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468493</v>
+        <v>468356</v>
       </c>
       <c r="R74" t="n">
-        <v>7078945</v>
+        <v>7077992</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8320,11 +8320,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8351,7 +8346,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119713661</v>
+        <v>119713654</v>
       </c>
       <c r="B75" t="n">
         <v>57310</v>
@@ -8391,10 +8386,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468387</v>
+        <v>468493</v>
       </c>
       <c r="R75" t="n">
-        <v>7078948</v>
+        <v>7078945</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8458,10 +8453,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119713687</v>
+        <v>119713661</v>
       </c>
       <c r="B76" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8474,21 +8469,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8498,10 +8493,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468461</v>
+        <v>468387</v>
       </c>
       <c r="R76" t="n">
-        <v>7078992</v>
+        <v>7078948</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8534,6 +8529,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -3091,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713705</v>
+        <v>119713676</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468432</v>
+        <v>468277</v>
       </c>
       <c r="R25" t="n">
-        <v>7078079</v>
+        <v>7078898</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713676</v>
+        <v>119713705</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,21 +3209,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468277</v>
+        <v>468432</v>
       </c>
       <c r="R26" t="n">
-        <v>7078898</v>
+        <v>7078079</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -3091,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713676</v>
+        <v>119713705</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468277</v>
+        <v>468432</v>
       </c>
       <c r="R25" t="n">
-        <v>7078898</v>
+        <v>7078079</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713705</v>
+        <v>119713676</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,21 +3209,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468432</v>
+        <v>468277</v>
       </c>
       <c r="R26" t="n">
-        <v>7078079</v>
+        <v>7078898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 36205-2024 artfynd.xlsx
+++ b/artfynd/A 36205-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713686</v>
+        <v>119713697</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468414</v>
+        <v>468436</v>
       </c>
       <c r="R2" t="n">
-        <v>7078890</v>
+        <v>7079043</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713708</v>
+        <v>119713695</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468354</v>
+        <v>468411</v>
       </c>
       <c r="R3" t="n">
-        <v>7078051</v>
+        <v>7078994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713706</v>
+        <v>119713665</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468414</v>
+        <v>468309</v>
       </c>
       <c r="R4" t="n">
-        <v>7078867</v>
+        <v>7079036</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713665</v>
+        <v>119713712</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>91146</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468309</v>
+        <v>468491</v>
       </c>
       <c r="R5" t="n">
-        <v>7079036</v>
+        <v>7078902</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713652</v>
+        <v>119713673</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468431</v>
+        <v>468436</v>
       </c>
       <c r="R6" t="n">
-        <v>7078899</v>
+        <v>7079043</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713633</v>
+        <v>119713632</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468383</v>
+        <v>468387</v>
       </c>
       <c r="R7" t="n">
-        <v>7078394</v>
+        <v>7078261</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713643</v>
+        <v>119713647</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468546</v>
+        <v>468481</v>
       </c>
       <c r="R8" t="n">
-        <v>7078893</v>
+        <v>7078859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713663</v>
+        <v>119713609</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468431</v>
+        <v>468506</v>
       </c>
       <c r="R9" t="n">
-        <v>7079071</v>
+        <v>7078126</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713682</v>
+        <v>119713710</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468392</v>
+        <v>468311</v>
       </c>
       <c r="R10" t="n">
-        <v>7078534</v>
+        <v>7079041</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1582,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713707</v>
+        <v>119713661</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468344</v>
+        <v>468387</v>
       </c>
       <c r="R11" t="n">
-        <v>7078143</v>
+        <v>7078948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1693,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713695</v>
+        <v>119713629</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468411</v>
+        <v>468444</v>
       </c>
       <c r="R12" t="n">
-        <v>7078994</v>
+        <v>7078147</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713613</v>
+        <v>119713681</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468269</v>
+        <v>468360</v>
       </c>
       <c r="R13" t="n">
-        <v>7079044</v>
+        <v>7078504</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713681</v>
+        <v>119713685</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468360</v>
+        <v>468491</v>
       </c>
       <c r="R14" t="n">
-        <v>7078504</v>
+        <v>7078903</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713641</v>
+        <v>119713686</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468546</v>
+        <v>468414</v>
       </c>
       <c r="R15" t="n">
-        <v>7078889</v>
+        <v>7078890</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,11 +2107,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713710</v>
+        <v>119713675</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468311</v>
+        <v>468269</v>
       </c>
       <c r="R16" t="n">
-        <v>7079041</v>
+        <v>7078942</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713677</v>
+        <v>119713687</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468207</v>
+        <v>468461</v>
       </c>
       <c r="R17" t="n">
-        <v>7078579</v>
+        <v>7078992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713648</v>
+        <v>119713662</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468397</v>
+        <v>468406</v>
       </c>
       <c r="R18" t="n">
-        <v>7078890</v>
+        <v>7078996</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713609</v>
+        <v>119713649</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2460,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468506</v>
+        <v>468392</v>
       </c>
       <c r="R19" t="n">
-        <v>7078126</v>
+        <v>7078891</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,6 +2520,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713685</v>
+        <v>119713654</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468491</v>
+        <v>468493</v>
       </c>
       <c r="R20" t="n">
-        <v>7078903</v>
+        <v>7078945</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,6 +2627,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713650</v>
+        <v>119713683</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2674,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468408</v>
+        <v>468440</v>
       </c>
       <c r="R21" t="n">
-        <v>7078892</v>
+        <v>7078819</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713618</v>
+        <v>119713680</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2776,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468315</v>
+        <v>468356</v>
       </c>
       <c r="R22" t="n">
-        <v>7078711</v>
+        <v>7078372</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,11 +2836,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713684</v>
+        <v>119713689</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468525</v>
+        <v>468428</v>
       </c>
       <c r="R23" t="n">
-        <v>7078870</v>
+        <v>7078967</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713625</v>
+        <v>119713616</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468255</v>
+        <v>468263</v>
       </c>
       <c r="R24" t="n">
-        <v>7078014</v>
+        <v>7078968</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3064,7 +3044,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3091,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713705</v>
+        <v>119713707</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468432</v>
+        <v>468344</v>
       </c>
       <c r="R25" t="n">
-        <v>7078079</v>
+        <v>7078143</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3167,6 +3147,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3193,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713676</v>
+        <v>119713646</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,21 +3194,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3233,10 +3218,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468277</v>
+        <v>468500</v>
       </c>
       <c r="R26" t="n">
-        <v>7078898</v>
+        <v>7078848</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3269,6 +3254,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119713626</v>
+        <v>119713637</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468396</v>
+        <v>468382</v>
       </c>
       <c r="R27" t="n">
-        <v>7078010</v>
+        <v>7078551</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,7 +3365,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3402,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713657</v>
+        <v>119713648</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3442,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468462</v>
+        <v>468397</v>
       </c>
       <c r="R28" t="n">
-        <v>7078991</v>
+        <v>7078890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713620</v>
+        <v>119713703</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,21 +3515,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3549,10 +3539,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468251</v>
+        <v>468369</v>
       </c>
       <c r="R29" t="n">
-        <v>7078667</v>
+        <v>7078973</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,11 +3575,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3616,10 +3601,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713628</v>
+        <v>119713711</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3656,10 +3641,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468442</v>
+        <v>468242</v>
       </c>
       <c r="R30" t="n">
-        <v>7078110</v>
+        <v>7079178</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3696,7 +3681,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3723,10 +3708,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713638</v>
+        <v>119713709</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,21 +3724,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3763,10 +3748,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468450</v>
+        <v>468530</v>
       </c>
       <c r="R31" t="n">
-        <v>7078735</v>
+        <v>7078853</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3803,7 +3788,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3830,10 +3815,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713612</v>
+        <v>119713636</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3870,10 +3855,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468171</v>
+        <v>468454</v>
       </c>
       <c r="R32" t="n">
-        <v>7079106</v>
+        <v>7078551</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3937,10 +3922,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713617</v>
+        <v>119713628</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3977,10 +3962,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468290</v>
+        <v>468442</v>
       </c>
       <c r="R33" t="n">
-        <v>7078881</v>
+        <v>7078110</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,10 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713647</v>
+        <v>119713623</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4084,10 +4069,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468481</v>
+        <v>468342</v>
       </c>
       <c r="R34" t="n">
-        <v>7078859</v>
+        <v>7078288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4124,7 +4109,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4151,10 +4136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713666</v>
+        <v>119713610</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4167,21 +4152,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4191,10 +4176,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>468267</v>
+        <v>468502</v>
       </c>
       <c r="R35" t="n">
-        <v>7079149</v>
+        <v>7078172</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4227,11 +4212,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4258,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119713631</v>
+        <v>119713635</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4298,10 +4278,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>468508</v>
+        <v>468498</v>
       </c>
       <c r="R36" t="n">
-        <v>7078150</v>
+        <v>7078513</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119713610</v>
+        <v>119713691</v>
       </c>
       <c r="B37" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4381,21 +4361,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4405,10 +4385,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>468502</v>
+        <v>468394</v>
       </c>
       <c r="R37" t="n">
-        <v>7078172</v>
+        <v>7078944</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119713680</v>
+        <v>119713684</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4507,10 +4487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468356</v>
+        <v>468525</v>
       </c>
       <c r="R38" t="n">
-        <v>7078372</v>
+        <v>7078870</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4572,7 +4552,7 @@
         <v>119713693</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4671,10 +4651,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119713692</v>
+        <v>119713627</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4687,21 +4667,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4711,10 +4691,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468377</v>
+        <v>468420</v>
       </c>
       <c r="R40" t="n">
-        <v>7078959</v>
+        <v>7078103</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,6 +4727,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119713694</v>
+        <v>119713611</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4789,21 +4774,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4813,10 +4798,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468358</v>
+        <v>468510</v>
       </c>
       <c r="R41" t="n">
-        <v>7078970</v>
+        <v>7078916</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4849,6 +4834,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4875,10 +4865,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119713709</v>
+        <v>119713630</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,21 +4881,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4905,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468530</v>
+        <v>468507</v>
       </c>
       <c r="R42" t="n">
-        <v>7078853</v>
+        <v>7078135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4955,7 +4945,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4982,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119713639</v>
+        <v>119713617</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5022,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468440</v>
+        <v>468290</v>
       </c>
       <c r="R43" t="n">
-        <v>7078822</v>
+        <v>7078881</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5062,7 +5052,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5089,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119713629</v>
+        <v>119713634</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5129,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468444</v>
+        <v>468498</v>
       </c>
       <c r="R44" t="n">
-        <v>7078147</v>
+        <v>7078528</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,7 +5159,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5196,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119713712</v>
+        <v>119713714</v>
       </c>
       <c r="B45" t="n">
-        <v>91128</v>
+        <v>86895</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5208,25 +5198,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>510</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468491</v>
+        <v>468340</v>
       </c>
       <c r="R45" t="n">
-        <v>7078902</v>
+        <v>7078142</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119713623</v>
+        <v>119713694</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5314,21 +5304,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5338,10 +5328,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468342</v>
+        <v>468358</v>
       </c>
       <c r="R46" t="n">
-        <v>7078288</v>
+        <v>7078970</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5374,11 +5364,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5405,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119713636</v>
+        <v>119713682</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5421,21 +5406,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5445,10 +5430,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468454</v>
+        <v>468392</v>
       </c>
       <c r="R47" t="n">
-        <v>7078551</v>
+        <v>7078534</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5481,11 +5466,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5512,10 +5492,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119713630</v>
+        <v>119713708</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5528,21 +5508,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5552,10 +5532,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468507</v>
+        <v>468354</v>
       </c>
       <c r="R48" t="n">
-        <v>7078135</v>
+        <v>7078051</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5592,7 +5572,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5619,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119713645</v>
+        <v>119713643</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5659,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468491</v>
+        <v>468546</v>
       </c>
       <c r="R49" t="n">
-        <v>7078873</v>
+        <v>7078893</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5726,10 +5706,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119713664</v>
+        <v>119713621</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5766,10 +5746,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468402</v>
+        <v>468270</v>
       </c>
       <c r="R50" t="n">
-        <v>7079059</v>
+        <v>7078423</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5806,7 +5786,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5833,10 +5813,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119713660</v>
+        <v>119713641</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5873,10 +5853,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468411</v>
+        <v>468546</v>
       </c>
       <c r="R51" t="n">
-        <v>7078960</v>
+        <v>7078889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5913,7 +5893,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5940,10 +5920,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119713624</v>
+        <v>119713664</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5980,10 +5960,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468284</v>
+        <v>468402</v>
       </c>
       <c r="R52" t="n">
-        <v>7078113</v>
+        <v>7079059</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6020,7 +6000,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6047,10 +6027,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119713622</v>
+        <v>119713652</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6087,10 +6067,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468259</v>
+        <v>468431</v>
       </c>
       <c r="R53" t="n">
-        <v>7078432</v>
+        <v>7078899</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6127,7 +6107,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6154,10 +6134,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119713675</v>
+        <v>119713625</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6170,21 +6150,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6194,10 +6174,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468269</v>
+        <v>468255</v>
       </c>
       <c r="R54" t="n">
-        <v>7078942</v>
+        <v>7078014</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6230,6 +6210,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6256,10 +6241,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119713691</v>
+        <v>119713677</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6296,10 +6281,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468394</v>
+        <v>468207</v>
       </c>
       <c r="R55" t="n">
-        <v>7078944</v>
+        <v>7078579</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6358,10 +6343,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119713632</v>
+        <v>119713613</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6398,10 +6383,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468387</v>
+        <v>468269</v>
       </c>
       <c r="R56" t="n">
-        <v>7078261</v>
+        <v>7079044</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6438,7 +6423,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6465,10 +6450,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119713640</v>
+        <v>119713633</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6505,10 +6490,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468538</v>
+        <v>468383</v>
       </c>
       <c r="R57" t="n">
-        <v>7078860</v>
+        <v>7078394</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6572,10 +6557,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119713683</v>
+        <v>119713663</v>
       </c>
       <c r="B58" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6588,21 +6573,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6612,10 +6597,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468440</v>
+        <v>468431</v>
       </c>
       <c r="R58" t="n">
-        <v>7078819</v>
+        <v>7079071</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6648,6 +6633,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6674,10 +6664,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119713697</v>
+        <v>119713660</v>
       </c>
       <c r="B59" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6690,21 +6680,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6714,10 +6704,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468436</v>
+        <v>468411</v>
       </c>
       <c r="R59" t="n">
-        <v>7079043</v>
+        <v>7078960</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6750,6 +6740,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6776,10 +6771,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119713616</v>
+        <v>119713620</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6816,10 +6811,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468263</v>
+        <v>468251</v>
       </c>
       <c r="R60" t="n">
-        <v>7078968</v>
+        <v>7078667</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6856,7 +6851,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6883,10 +6878,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119713646</v>
+        <v>119713640</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6923,10 +6918,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468500</v>
+        <v>468538</v>
       </c>
       <c r="R61" t="n">
-        <v>7078848</v>
+        <v>7078860</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6963,7 +6958,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6990,10 +6985,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119713621</v>
+        <v>119713639</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7030,10 +7025,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468270</v>
+        <v>468440</v>
       </c>
       <c r="R62" t="n">
-        <v>7078423</v>
+        <v>7078822</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7097,10 +7092,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119713673</v>
+        <v>119713698</v>
       </c>
       <c r="B63" t="n">
-        <v>79608</v>
+        <v>79623</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7113,21 +7108,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7137,10 +7132,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468436</v>
+        <v>468338</v>
       </c>
       <c r="R63" t="n">
-        <v>7079043</v>
+        <v>7079023</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7199,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119713703</v>
+        <v>119713666</v>
       </c>
       <c r="B64" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7215,21 +7210,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7239,10 +7234,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468369</v>
+        <v>468267</v>
       </c>
       <c r="R64" t="n">
-        <v>7078973</v>
+        <v>7079149</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7275,6 +7270,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7301,10 +7301,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119713699</v>
+        <v>119713657</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7317,21 +7317,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468287</v>
+        <v>468462</v>
       </c>
       <c r="R65" t="n">
-        <v>7079069</v>
+        <v>7078991</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7377,6 +7377,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7403,10 +7408,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119713714</v>
+        <v>119713638</v>
       </c>
       <c r="B66" t="n">
-        <v>86878</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7419,21 +7424,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7443,10 +7448,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468340</v>
+        <v>468450</v>
       </c>
       <c r="R66" t="n">
-        <v>7078142</v>
+        <v>7078735</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7479,6 +7484,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7505,10 +7515,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119713711</v>
+        <v>119713626</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7521,21 +7531,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7545,10 +7555,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468242</v>
+        <v>468396</v>
       </c>
       <c r="R67" t="n">
-        <v>7079178</v>
+        <v>7078010</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7585,7 +7595,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7612,10 +7622,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119713637</v>
+        <v>119713705</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7628,21 +7638,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7652,10 +7662,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468382</v>
+        <v>468432</v>
       </c>
       <c r="R68" t="n">
-        <v>7078551</v>
+        <v>7078079</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7688,11 +7698,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7722,7 +7727,7 @@
         <v>119713614</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7826,10 +7831,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119713611</v>
+        <v>119713667</v>
       </c>
       <c r="B70" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7866,10 +7871,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468510</v>
+        <v>468260</v>
       </c>
       <c r="R70" t="n">
-        <v>7078916</v>
+        <v>7079151</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7906,7 +7911,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7933,10 +7938,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119713634</v>
+        <v>119713650</v>
       </c>
       <c r="B71" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7973,10 +7978,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468498</v>
+        <v>468408</v>
       </c>
       <c r="R71" t="n">
-        <v>7078528</v>
+        <v>7078892</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8013,7 +8018,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8040,10 +8045,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119713678</v>
+        <v>119713618</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8056,21 +8061,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8080,10 +8085,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468305</v>
+        <v>468315</v>
       </c>
       <c r="R72" t="n">
-        <v>7078326</v>
+        <v>7078711</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8116,6 +8121,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8142,10 +8152,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119713687</v>
+        <v>119713631</v>
       </c>
       <c r="B73" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8158,21 +8168,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8182,10 +8192,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468461</v>
+        <v>468508</v>
       </c>
       <c r="R73" t="n">
-        <v>7078992</v>
+        <v>7078150</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8218,6 +8228,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8244,10 +8259,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119713704</v>
+        <v>119713612</v>
       </c>
       <c r="B74" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8260,21 +8275,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8284,10 +8299,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468356</v>
+        <v>468171</v>
       </c>
       <c r="R74" t="n">
-        <v>7077992</v>
+        <v>7079106</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8320,6 +8335,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8346,10 +8366,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119713654</v>
+        <v>119713679</v>
       </c>
       <c r="B75" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8362,21 +8382,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8386,10 +8406,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468493</v>
+        <v>468408</v>
       </c>
       <c r="R75" t="n">
-        <v>7078945</v>
+        <v>7078270</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8422,11 +8442,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8453,10 +8468,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119713661</v>
+        <v>119713676</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8469,21 +8484,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8493,10 +8508,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468387</v>
+        <v>468277</v>
       </c>
       <c r="R76" t="n">
-        <v>7078948</v>
+        <v>7078898</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,11 +8544,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8560,10 +8570,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119713689</v>
+        <v>119713678</v>
       </c>
       <c r="B77" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8600,10 +8610,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468428</v>
+        <v>468305</v>
       </c>
       <c r="R77" t="n">
-        <v>7078967</v>
+        <v>7078326</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8662,10 +8672,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119713679</v>
+        <v>119713692</v>
       </c>
       <c r="B78" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8702,10 +8712,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468408</v>
+        <v>468377</v>
       </c>
       <c r="R78" t="n">
-        <v>7078270</v>
+        <v>7078959</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8764,10 +8774,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119713698</v>
+        <v>119713699</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8804,10 +8814,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468338</v>
+        <v>468287</v>
       </c>
       <c r="R79" t="n">
-        <v>7079023</v>
+        <v>7079069</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8866,10 +8876,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119713649</v>
+        <v>119713706</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8882,21 +8892,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8906,10 +8916,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468392</v>
+        <v>468414</v>
       </c>
       <c r="R80" t="n">
-        <v>7078891</v>
+        <v>7078867</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8942,11 +8952,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8973,10 +8978,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119713667</v>
+        <v>119713704</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8989,21 +8994,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9013,10 +9018,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468260</v>
+        <v>468356</v>
       </c>
       <c r="R81" t="n">
-        <v>7079151</v>
+        <v>7077992</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9049,11 +9054,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9080,10 +9080,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119713627</v>
+        <v>119713624</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468420</v>
+        <v>468284</v>
       </c>
       <c r="R82" t="n">
-        <v>7078103</v>
+        <v>7078113</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9187,10 +9187,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119713635</v>
+        <v>119713645</v>
       </c>
       <c r="B83" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468498</v>
+        <v>468491</v>
       </c>
       <c r="R83" t="n">
-        <v>7078513</v>
+        <v>7078873</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9294,10 +9294,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119713662</v>
+        <v>119713622</v>
       </c>
       <c r="B84" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9334,10 +9334,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468406</v>
+        <v>468259</v>
       </c>
       <c r="R84" t="n">
-        <v>7078996</v>
+        <v>7078432</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
